--- a/sormas-base/doc/SormasDictionary.xlsx
+++ b/sormas-base/doc/SormasDictionary.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="723">
   <si>
     <t>Field</t>
   </si>
@@ -50,6 +50,45 @@
     <t>Outbreaks</t>
   </si>
   <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>First name</t>
+  </si>
+  <si>
+    <t>Enter the first name of the person</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>Last name</t>
+  </si>
+  <si>
+    <t>Enter the last name of the person</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>Nickname</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>mothersMaidenName</t>
+  </si>
+  <si>
+    <t>Mother's maiden name</t>
+  </si>
+  <si>
     <t>sex</t>
   </si>
   <si>
@@ -62,28 +101,34 @@
     <t>Select the sex of the person</t>
   </si>
   <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>firstName</t>
-  </si>
-  <si>
-    <t>Text</t>
-  </si>
-  <si>
-    <t>First name</t>
-  </si>
-  <si>
-    <t>Enter the first name of the person</t>
-  </si>
-  <si>
-    <t>lastName</t>
-  </si>
-  <si>
-    <t>Last name</t>
-  </si>
-  <si>
-    <t>Enter the last name of the person</t>
+    <t>birthdateDD</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>birthdateMM</t>
+  </si>
+  <si>
+    <t>birthdateYYYY</t>
+  </si>
+  <si>
+    <t>approximateAge</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Enter the age of the person</t>
+  </si>
+  <si>
+    <t>approximateAgeType</t>
+  </si>
+  <si>
+    <t>YEARS, MONTHS</t>
+  </si>
+  <si>
+    <t>Unit</t>
   </si>
   <si>
     <t>presentCondition</t>
@@ -98,39 +143,6 @@
     <t>Select the person's current health condition</t>
   </si>
   <si>
-    <t>birthdateDD</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>birthdateMM</t>
-  </si>
-  <si>
-    <t>birthdateYYYY</t>
-  </si>
-  <si>
-    <t>approximateAge</t>
-  </si>
-  <si>
-    <t>Age</t>
-  </si>
-  <si>
-    <t>Enter the age of the person</t>
-  </si>
-  <si>
-    <t>approximateAgeType</t>
-  </si>
-  <si>
-    <t>YEARS, MONTHS</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
     <t>deathDate</t>
   </si>
   <si>
@@ -206,18 +218,6 @@
     <t>Burial conductor</t>
   </si>
   <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>Nickname</t>
-  </si>
-  <si>
-    <t>mothersMaidenName</t>
-  </si>
-  <si>
-    <t>Mother's maiden name</t>
-  </si>
-  <si>
     <t>phone</t>
   </si>
   <si>
@@ -299,6 +299,24 @@
     <t>Health facility name &amp; description</t>
   </si>
   <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>district</t>
+  </si>
+  <si>
+    <t>LGA</t>
+  </si>
+  <si>
+    <t>community</t>
+  </si>
+  <si>
+    <t>Ward</t>
+  </si>
+  <si>
     <t>Address or landmark</t>
   </si>
   <si>
@@ -314,24 +332,6 @@
     <t>City</t>
   </si>
   <si>
-    <t>region</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>district</t>
-  </si>
-  <si>
-    <t>LGA</t>
-  </si>
-  <si>
-    <t>community</t>
-  </si>
-  <si>
-    <t>Ward</t>
-  </si>
-  <si>
     <t>latitude</t>
   </si>
   <si>
@@ -359,6 +359,66 @@
     <t>If you draw a circle centered at this location's latitude and longitude, and with a radius equal to the accuracy, then there is a 68% probability that the true location is inside the circle</t>
   </si>
   <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>Disease</t>
+  </si>
+  <si>
+    <t>Select the disease in question</t>
+  </si>
+  <si>
+    <t>diseaseDetails</t>
+  </si>
+  <si>
+    <t>Disease name</t>
+  </si>
+  <si>
+    <t>plagueType</t>
+  </si>
+  <si>
+    <t>BUBONIC, PNEUMONIC, SEPTICAEMIC</t>
+  </si>
+  <si>
+    <t>Plague type</t>
+  </si>
+  <si>
+    <t>Plague</t>
+  </si>
+  <si>
+    <t>dengueFeverType</t>
+  </si>
+  <si>
+    <t>DENGUE_FEVER, DENGUE_HEMORRHAGIC_FEVER, DENUGE_SHOCK_SYNDROME</t>
+  </si>
+  <si>
+    <t>Dengue fever type</t>
+  </si>
+  <si>
+    <t>Dengue</t>
+  </si>
+  <si>
+    <t>person</t>
+  </si>
+  <si>
+    <t>PersonReference</t>
+  </si>
+  <si>
+    <t>Case person</t>
+  </si>
+  <si>
+    <t>epidNumber</t>
+  </si>
+  <si>
+    <t>EPID number</t>
+  </si>
+  <si>
+    <t>reportDate</t>
+  </si>
+  <si>
+    <t>Date of report</t>
+  </si>
+  <si>
     <t>reportingUser</t>
   </si>
   <si>
@@ -368,19 +428,13 @@
     <t>Reporting user</t>
   </si>
   <si>
-    <t>reportDate</t>
-  </si>
-  <si>
-    <t>Date of report</t>
-  </si>
-  <si>
-    <t>person</t>
-  </si>
-  <si>
-    <t>PersonReference</t>
-  </si>
-  <si>
-    <t>Case person</t>
+    <t>receptionDate</t>
+  </si>
+  <si>
+    <t>Date of reception</t>
+  </si>
+  <si>
+    <t>Date the case information was received at the state or national level</t>
   </si>
   <si>
     <t>caseClassification</t>
@@ -410,45 +464,6 @@
     <t>classificationComment</t>
   </si>
   <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>Disease</t>
-  </si>
-  <si>
-    <t>Select the disease in question</t>
-  </si>
-  <si>
-    <t>diseaseDetails</t>
-  </si>
-  <si>
-    <t>Disease name</t>
-  </si>
-  <si>
-    <t>plagueType</t>
-  </si>
-  <si>
-    <t>BUBONIC, PNEUMONIC, SEPTICAEMIC</t>
-  </si>
-  <si>
-    <t>Plague type</t>
-  </si>
-  <si>
-    <t>Plague</t>
-  </si>
-  <si>
-    <t>dengueFeverType</t>
-  </si>
-  <si>
-    <t>DENGUE_FEVER, DENGUE_HEMORRHAGIC_FEVER, DENUGE_SHOCK_SYNDROME</t>
-  </si>
-  <si>
-    <t>Dengue fever type</t>
-  </si>
-  <si>
-    <t>Dengue</t>
-  </si>
-  <si>
     <t>investigationStatus</t>
   </si>
   <si>
@@ -464,13 +479,118 @@
     <t>Date of investigation</t>
   </si>
   <si>
-    <t>receptionDate</t>
-  </si>
-  <si>
-    <t>Date of reception</t>
-  </si>
-  <si>
-    <t>Date the case information was received at the state or national level</t>
+    <t>outcome</t>
+  </si>
+  <si>
+    <t>NO_OUTCOME, DECEASED, RECOVERED, UNKNOWN</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>outcomeDate</t>
+  </si>
+  <si>
+    <t>Date of outcome</t>
+  </si>
+  <si>
+    <t>healthFacility</t>
+  </si>
+  <si>
+    <t>Health facility</t>
+  </si>
+  <si>
+    <t>Provide the name of the health facility the patient was admitted</t>
+  </si>
+  <si>
+    <t>healthFacilityDetails</t>
+  </si>
+  <si>
+    <t>pregnant</t>
+  </si>
+  <si>
+    <t>YES, NO, UNKNOWN</t>
+  </si>
+  <si>
+    <t>Pregnancy</t>
+  </si>
+  <si>
+    <t>Is the person currently pregnant?</t>
+  </si>
+  <si>
+    <t>vaccination</t>
+  </si>
+  <si>
+    <t>VACCINATED, UNVACCINATED, UNKNOWN</t>
+  </si>
+  <si>
+    <t>Vaccination status for this disease</t>
+  </si>
+  <si>
+    <t>Measles, Yellow fever, CSM, Other</t>
+  </si>
+  <si>
+    <t>vaccinationDoses</t>
+  </si>
+  <si>
+    <t>Number of valid doses</t>
+  </si>
+  <si>
+    <t>Measles, CSM, Other</t>
+  </si>
+  <si>
+    <t>vaccinationDate</t>
+  </si>
+  <si>
+    <t>Date of last vaccination</t>
+  </si>
+  <si>
+    <t>Measles, Yellow fever, CSM, Monkeypox, Other</t>
+  </si>
+  <si>
+    <t>vaccinationInfoSource</t>
+  </si>
+  <si>
+    <t>VACCINATION_CARD, ORAL_COMMUNICATION</t>
+  </si>
+  <si>
+    <t>Source of vaccination information</t>
+  </si>
+  <si>
+    <t>smallpoxVaccinationScar</t>
+  </si>
+  <si>
+    <t>Is a Smallpox vaccination scar present?</t>
+  </si>
+  <si>
+    <t>Monkeypox</t>
+  </si>
+  <si>
+    <t>smallpoxVaccinationReceived</t>
+  </si>
+  <si>
+    <t>Was a Smallpox vaccination received in the past?</t>
+  </si>
+  <si>
+    <t>surveillanceOfficer</t>
+  </si>
+  <si>
+    <t>Responsible surveillance officer</t>
+  </si>
+  <si>
+    <t>caseOfficer</t>
+  </si>
+  <si>
+    <t>Case officer</t>
+  </si>
+  <si>
+    <t>reportLat</t>
+  </si>
+  <si>
+    <t>reportLon</t>
+  </si>
+  <si>
+    <t>reportLatLonAccuracy</t>
   </si>
   <si>
     <t>hospitalization</t>
@@ -479,6 +599,12 @@
     <t>Hospitalization</t>
   </si>
   <si>
+    <t>symptoms</t>
+  </si>
+  <si>
+    <t>Symptoms</t>
+  </si>
+  <si>
     <t>epiData</t>
   </si>
   <si>
@@ -488,130 +614,10 @@
     <t>Epidemiological data</t>
   </si>
   <si>
-    <t>healthFacility</t>
-  </si>
-  <si>
-    <t>Health facility</t>
-  </si>
-  <si>
-    <t>Provide the name of the health facility the patient was admitted</t>
-  </si>
-  <si>
-    <t>healthFacilityDetails</t>
-  </si>
-  <si>
-    <t>symptoms</t>
-  </si>
-  <si>
-    <t>Symptoms</t>
-  </si>
-  <si>
-    <t>pregnant</t>
-  </si>
-  <si>
-    <t>YES, NO, UNKNOWN</t>
-  </si>
-  <si>
-    <t>Pregnancy</t>
-  </si>
-  <si>
-    <t>Is the person currently pregnant?</t>
-  </si>
-  <si>
-    <t>vaccination</t>
-  </si>
-  <si>
-    <t>VACCINATED, UNVACCINATED, UNKNOWN</t>
-  </si>
-  <si>
-    <t>Vaccination status for this disease</t>
-  </si>
-  <si>
-    <t>Measles, Yellow fever, CSM, Other</t>
-  </si>
-  <si>
-    <t>vaccinationDoses</t>
-  </si>
-  <si>
-    <t>Number of valid doses</t>
-  </si>
-  <si>
-    <t>Measles, CSM, Other</t>
-  </si>
-  <si>
-    <t>vaccinationDate</t>
-  </si>
-  <si>
-    <t>Date of last vaccination</t>
-  </si>
-  <si>
-    <t>Measles, Yellow fever, CSM, Monkeypox, Other</t>
-  </si>
-  <si>
-    <t>vaccinationInfoSource</t>
-  </si>
-  <si>
-    <t>VACCINATION_CARD, ORAL_COMMUNICATION</t>
-  </si>
-  <si>
-    <t>Source of vaccination information</t>
-  </si>
-  <si>
-    <t>smallpoxVaccinationScar</t>
-  </si>
-  <si>
-    <t>Is a Smallpox vaccination scar present?</t>
-  </si>
-  <si>
-    <t>Monkeypox</t>
-  </si>
-  <si>
-    <t>smallpoxVaccinationReceived</t>
-  </si>
-  <si>
-    <t>Was a Smallpox vaccination received in the past?</t>
-  </si>
-  <si>
-    <t>epidNumber</t>
-  </si>
-  <si>
-    <t>EPID number</t>
-  </si>
-  <si>
-    <t>surveillanceOfficer</t>
-  </si>
-  <si>
-    <t>Responsible surveillance officer</t>
-  </si>
-  <si>
-    <t>caseOfficer</t>
-  </si>
-  <si>
-    <t>Case officer</t>
-  </si>
-  <si>
-    <t>reportLat</t>
-  </si>
-  <si>
-    <t>reportLon</t>
-  </si>
-  <si>
-    <t>reportLatLonAccuracy</t>
-  </si>
-  <si>
-    <t>outcome</t>
-  </si>
-  <si>
-    <t>NO_OUTCOME, DECEASED, RECOVERED, UNKNOWN</t>
-  </si>
-  <si>
-    <t>Outcome</t>
-  </si>
-  <si>
-    <t>outcomeDate</t>
-  </si>
-  <si>
-    <t>Date of outcome</t>
+    <t>admittedToHealthFacility</t>
+  </si>
+  <si>
+    <t>Was patient admitted at the health facility?</t>
   </si>
   <si>
     <t>admissionDate</t>
@@ -650,12 +656,6 @@
     <t>Was the patient hospitalized or did he/she visit a health clinic previously for this illness?</t>
   </si>
   <si>
-    <t>admittedToHealthFacility</t>
-  </si>
-  <si>
-    <t>Was patient admitted at the health facility?</t>
-  </si>
-  <si>
     <t>previousHospitalizations</t>
   </si>
   <si>
@@ -1733,6 +1733,9 @@
     <t>Follow-up status</t>
   </si>
   <si>
+    <t>Under follow-up: The follow-up process is running. Follow-up completed: The follow-up has been completed. Follow-up canceled: The follow-up process has been canceled, e.g. because the person died or the contact became irrelevant. Lost to follow-up: The follow-up process could not be continued because the person was not available. No follow-up: No contact follow-up is being done.</t>
+  </si>
+  <si>
     <t>EVD, Lassa, Cholera, Monkeypox, Plague, Other</t>
   </si>
   <si>
@@ -2127,15 +2130,6 @@
   </si>
   <si>
     <t>Name</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>District</t>
-  </si>
-  <si>
-    <t>Community</t>
   </si>
   <si>
     <t>Latitude</t>
@@ -2294,7 +2288,9 @@
       <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2"/>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
       <c r="F2" t="s">
         <v>11</v>
       </c>
@@ -2307,13 +2303,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -2327,60 +2323,54 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
       <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E4"/>
       <c r="F4" t="s">
         <v>11</v>
       </c>
-      <c r="G4" t="b">
-        <v>1</v>
-      </c>
+      <c r="G4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="s">
         <v>11</v>
       </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
+      <c r="G5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
         <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
@@ -2392,16 +2382,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
@@ -2413,16 +2403,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
@@ -2434,16 +2424,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E9"/>
       <c r="F9" t="s">
@@ -2455,16 +2445,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
@@ -2476,54 +2466,58 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
         <v>11</v>
       </c>
-      <c r="G11"/>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
         <v>11</v>
       </c>
-      <c r="G12"/>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
         <v>41</v>
-      </c>
-      <c r="B13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
       </c>
       <c r="E13"/>
       <c r="F13" t="s">
@@ -2533,16 +2527,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
         <v>44</v>
       </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E14"/>
       <c r="F14" t="s">
@@ -2552,58 +2546,58 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
         <v>46</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>47</v>
       </c>
-      <c r="C15" t="s">
-        <v>48</v>
-      </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E15"/>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="G15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="G16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
         <v>52</v>
       </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>53</v>
-      </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G17"/>
     </row>
@@ -2612,17 +2606,17 @@
         <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C18" t="s">
         <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E18"/>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G18"/>
     </row>
@@ -2631,55 +2625,55 @@
         <v>56</v>
       </c>
       <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
         <v>57</v>
       </c>
-      <c r="C19" t="s">
-        <v>58</v>
-      </c>
       <c r="D19" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E19"/>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
         <v>59</v>
       </c>
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
       <c r="D20" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E20"/>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="G20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
         <v>61</v>
-      </c>
-      <c r="B21" t="s">
-        <v>13</v>
       </c>
       <c r="C21" t="s">
         <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E21"/>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="G21"/>
     </row>
@@ -2688,7 +2682,7 @@
         <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C22" t="s">
         <v>64</v>
@@ -2707,13 +2701,13 @@
         <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C23" t="s">
         <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E23"/>
       <c r="F23" t="s">
@@ -2732,7 +2726,7 @@
         <v>70</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E24"/>
       <c r="F24" t="s">
@@ -2751,7 +2745,7 @@
         <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E25"/>
       <c r="F25" t="s">
@@ -2764,13 +2758,13 @@
         <v>74</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C26" t="s">
         <v>75</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E26"/>
       <c r="F26" t="s">
@@ -2789,7 +2783,7 @@
         <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E27"/>
       <c r="F27" t="s">
@@ -2808,7 +2802,7 @@
         <v>81</v>
       </c>
       <c r="D28" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E28"/>
       <c r="F28" t="s">
@@ -2827,7 +2821,7 @@
         <v>84</v>
       </c>
       <c r="D29" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E29"/>
       <c r="F29" t="s">
@@ -2846,7 +2840,7 @@
         <v>87</v>
       </c>
       <c r="D30" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E30"/>
       <c r="F30" t="s">
@@ -2859,13 +2853,13 @@
         <v>88</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C31" t="s">
         <v>89</v>
       </c>
       <c r="D31" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E31"/>
       <c r="F31" t="s">
@@ -2917,16 +2911,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -2938,16 +2932,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C3" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -2959,16 +2953,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
@@ -2978,16 +2972,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D5" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -2999,16 +2993,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B6" t="s">
         <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -3020,16 +3014,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
@@ -3039,16 +3033,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -3060,16 +3054,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C9" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -3081,16 +3075,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -3102,16 +3096,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B11" t="s">
         <v>212</v>
       </c>
       <c r="C11" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
@@ -3121,16 +3115,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B12" t="s">
         <v>212</v>
       </c>
       <c r="C12" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D12" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
@@ -3182,16 +3176,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -3209,10 +3203,10 @@
         <v>549</v>
       </c>
       <c r="C3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
@@ -3222,16 +3216,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B4" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C4" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
@@ -3241,16 +3235,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B5" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C5" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="s">
@@ -3260,16 +3254,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B6" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C6" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D6" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -3281,16 +3275,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B7" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C7" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
@@ -3300,16 +3294,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -3321,16 +3315,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E9"/>
       <c r="F9" t="s">
@@ -3340,16 +3334,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B10" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C10" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
@@ -3359,16 +3353,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
@@ -3378,16 +3372,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
@@ -3397,16 +3391,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C13" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E13"/>
       <c r="F13" t="s">
@@ -3416,16 +3410,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E14"/>
       <c r="F14" t="s">
@@ -3435,16 +3429,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C15" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
@@ -3456,16 +3450,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
@@ -3475,16 +3469,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
@@ -3494,16 +3488,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E18"/>
       <c r="F18" t="s">
@@ -3513,16 +3507,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E19"/>
       <c r="F19" t="s">
@@ -3574,16 +3568,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="s">
@@ -3593,16 +3587,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
         <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>700</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
@@ -3612,16 +3606,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
         <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>701</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
@@ -3631,16 +3625,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s">
         <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>702</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="s">
@@ -3650,16 +3644,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
@@ -3672,13 +3666,13 @@
         <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
@@ -3691,13 +3685,13 @@
         <v>104</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
@@ -3707,16 +3701,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B9" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E9"/>
       <c r="F9" t="s">
@@ -3726,16 +3720,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B10" t="s">
         <v>212</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
@@ -3787,16 +3781,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B2" t="s">
         <v>212</v>
       </c>
       <c r="C2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="s">
@@ -3806,16 +3800,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
@@ -3825,16 +3819,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
@@ -3844,16 +3838,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="s">
@@ -3863,16 +3857,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
@@ -3885,13 +3879,13 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
@@ -3907,10 +3901,10 @@
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
@@ -3920,14 +3914,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B9"/>
       <c r="C9" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E9"/>
       <c r="F9" t="s">
@@ -3937,16 +3931,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B10" t="s">
         <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
@@ -3956,16 +3950,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
         <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
@@ -3975,16 +3969,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s">
         <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
@@ -3994,16 +3988,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B13" t="s">
         <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E13"/>
       <c r="F13" t="s">
@@ -4013,16 +4007,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C14" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E14"/>
       <c r="F14" t="s">
@@ -4074,16 +4068,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="s">
@@ -4093,16 +4087,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
@@ -4112,16 +4106,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
@@ -4131,16 +4125,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="s">
@@ -4192,16 +4186,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="s">
@@ -4211,16 +4205,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
@@ -4230,16 +4224,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
@@ -4249,16 +4243,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="s">
@@ -4268,16 +4262,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>700</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
@@ -4329,16 +4323,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="s">
@@ -4348,16 +4342,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
         <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>701</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
@@ -4409,16 +4403,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="s">
@@ -4428,16 +4422,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
@@ -4447,16 +4441,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
@@ -4466,16 +4460,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="s">
@@ -4488,13 +4482,13 @@
         <v>97</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
         <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
@@ -4507,13 +4501,13 @@
         <v>99</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
@@ -4526,7 +4520,7 @@
         <v>101</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
         <v>102</v>
@@ -4545,7 +4539,7 @@
         <v>104</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
         <v>105</v>
@@ -4564,7 +4558,7 @@
         <v>107</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
         <v>108</v>
@@ -4625,13 +4619,13 @@
         <v>110</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
         <v>111</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>112</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -4648,17 +4642,15 @@
         <v>113</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E3"/>
       <c r="F3" t="s">
         <v>11</v>
       </c>
@@ -4677,34 +4669,32 @@
         <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E4"/>
       <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4"/>
+        <v>118</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E5"/>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>122</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -4712,37 +4702,37 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6"/>
+        <v>17</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
       <c r="F6" t="s">
         <v>11</v>
       </c>
-      <c r="G6" t="b">
-        <v>1</v>
-      </c>
+      <c r="G6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
@@ -4754,18 +4744,20 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>129</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8"/>
+        <v>17</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
       <c r="F8" t="s">
         <v>11</v>
       </c>
@@ -4775,16 +4767,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -4798,16 +4790,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
@@ -4819,20 +4811,22 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11"/>
+        <v>139</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
       <c r="F11" t="s">
-        <v>135</v>
+        <v>11</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -4840,20 +4834,20 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
-        <v>139</v>
+        <v>11</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -4861,20 +4855,18 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B13" t="s">
-        <v>141</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E13"/>
       <c r="F13" t="s">
         <v>11</v>
       </c>
@@ -4884,16 +4876,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>144</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E14"/>
       <c r="F14" t="s">
@@ -4908,15 +4900,17 @@
         <v>145</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="C15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D15" t="s">
-        <v>147</v>
-      </c>
-      <c r="E15"/>
+        <v>17</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
       <c r="F15" t="s">
         <v>11</v>
       </c>
@@ -4929,19 +4923,21 @@
         <v>148</v>
       </c>
       <c r="B16" t="s">
-        <v>149</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
         <v>149</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
         <v>11</v>
       </c>
-      <c r="G16"/>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -4954,30 +4950,30 @@
         <v>152</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
         <v>11</v>
       </c>
-      <c r="G17"/>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E18"/>
       <c r="F18" t="s">
         <v>11</v>
       </c>
@@ -4987,16 +4983,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
@@ -5010,18 +5006,20 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20"/>
+        <v>17</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
       <c r="F20" t="s">
         <v>11</v>
       </c>
@@ -5031,20 +5029,18 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>153</v>
+        <v>94</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E21" t="b">
-        <v>1</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E21"/>
       <c r="F21" t="s">
         <v>11</v>
       </c>
@@ -5054,18 +5050,20 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" t="s">
         <v>156</v>
       </c>
-      <c r="B22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" t="s">
-        <v>89</v>
-      </c>
       <c r="D22" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22"/>
+        <v>157</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
       <c r="F22" t="s">
         <v>11</v>
       </c>
@@ -5075,22 +5073,24 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B23" t="s">
-        <v>158</v>
+        <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E23"/>
       <c r="F23" t="s">
         <v>11</v>
       </c>
-      <c r="G23"/>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
@@ -5122,7 +5122,7 @@
         <v>165</v>
       </c>
       <c r="D25" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E25"/>
       <c r="F25" t="s">
@@ -5137,13 +5137,13 @@
         <v>167</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C26" t="s">
         <v>168</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E26"/>
       <c r="F26" t="s">
@@ -5158,13 +5158,13 @@
         <v>170</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
         <v>171</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E27"/>
       <c r="F27" t="s">
@@ -5185,7 +5185,7 @@
         <v>175</v>
       </c>
       <c r="D28" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E28"/>
       <c r="F28" t="s">
@@ -5204,7 +5204,7 @@
         <v>177</v>
       </c>
       <c r="D29" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E29"/>
       <c r="F29" t="s">
@@ -5223,7 +5223,7 @@
         <v>180</v>
       </c>
       <c r="D30" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E30"/>
       <c r="F30" t="s">
@@ -5236,13 +5236,13 @@
         <v>181</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="C31" t="s">
         <v>182</v>
       </c>
       <c r="D31" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E31"/>
       <c r="F31" t="s">
@@ -5257,34 +5257,32 @@
         <v>183</v>
       </c>
       <c r="B32" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C32" t="s">
         <v>184</v>
       </c>
       <c r="D32" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E32"/>
       <c r="F32" t="s">
         <v>11</v>
       </c>
-      <c r="G32" t="b">
-        <v>1</v>
-      </c>
+      <c r="G32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
         <v>185</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>186</v>
+        <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E33"/>
       <c r="F33" t="s">
@@ -5294,16 +5292,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D34" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E34"/>
       <c r="F34" t="s">
@@ -5313,16 +5311,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E35"/>
       <c r="F35" t="s">
@@ -5332,16 +5330,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>188</v>
+      </c>
+      <c r="B36" t="s">
         <v>189</v>
       </c>
-      <c r="B36" t="s">
-        <v>24</v>
-      </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>189</v>
       </c>
       <c r="D36" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E36"/>
       <c r="F36" t="s">
@@ -5357,39 +5355,35 @@
         <v>191</v>
       </c>
       <c r="C37" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D37" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E37"/>
       <c r="F37" t="s">
         <v>11</v>
       </c>
-      <c r="G37" t="b">
-        <v>1</v>
-      </c>
+      <c r="G37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>192</v>
+      </c>
+      <c r="B38" t="s">
         <v>193</v>
-      </c>
-      <c r="B38" t="s">
-        <v>35</v>
       </c>
       <c r="C38" t="s">
         <v>194</v>
       </c>
       <c r="D38" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E38"/>
       <c r="F38" t="s">
         <v>11</v>
       </c>
-      <c r="G38" t="b">
-        <v>1</v>
-      </c>
+      <c r="G38"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -5438,13 +5432,13 @@
         <v>195</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s">
         <v>196</v>
       </c>
       <c r="D2" t="s">
-        <v>197</v>
+        <v>17</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="s">
@@ -5456,16 +5450,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
         <v>198</v>
       </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>199</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
@@ -5478,13 +5472,13 @@
         <v>200</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
         <v>201</v>
       </c>
       <c r="D4" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
@@ -5494,16 +5488,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" t="s">
         <v>203</v>
       </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>204</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="s">
@@ -5516,13 +5510,13 @@
         <v>205</v>
       </c>
       <c r="B6" t="s">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
         <v>206</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
@@ -5541,7 +5535,7 @@
         <v>208</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
@@ -5558,7 +5552,7 @@
         <v>210</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
@@ -5632,7 +5626,7 @@
         <v>215</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
         <v>216</v>
@@ -5653,7 +5647,7 @@
         <v>218</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>219</v>
@@ -5672,7 +5666,7 @@
         <v>221</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>222</v>
@@ -5741,7 +5735,7 @@
         <v>233</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
@@ -5783,7 +5777,7 @@
         <v>239</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
@@ -5821,7 +5815,7 @@
         <v>246</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
@@ -5840,7 +5834,7 @@
         <v>248</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E13"/>
       <c r="F13" t="s">
@@ -5861,7 +5855,7 @@
         <v>251</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E14"/>
       <c r="F14" t="s">
@@ -5882,7 +5876,7 @@
         <v>254</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E15"/>
       <c r="F15" t="s">
@@ -5901,7 +5895,7 @@
         <v>257</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
@@ -5983,7 +5977,7 @@
         <v>270</v>
       </c>
       <c r="D20" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E20"/>
       <c r="F20" t="s">
@@ -6002,7 +5996,7 @@
         <v>273</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E21"/>
       <c r="F21" t="s">
@@ -6021,7 +6015,7 @@
         <v>276</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E22"/>
       <c r="F22" t="s">
@@ -6040,7 +6034,7 @@
         <v>278</v>
       </c>
       <c r="D23" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E23"/>
       <c r="F23" t="s">
@@ -6059,7 +6053,7 @@
         <v>281</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E24"/>
       <c r="F24" t="s">
@@ -6078,7 +6072,7 @@
         <v>284</v>
       </c>
       <c r="D25" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E25"/>
       <c r="F25" t="s">
@@ -6097,7 +6091,7 @@
         <v>286</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E26"/>
       <c r="F26" t="s">
@@ -6116,7 +6110,7 @@
         <v>289</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E27"/>
       <c r="F27" t="s">
@@ -6135,7 +6129,7 @@
         <v>291</v>
       </c>
       <c r="D28" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E28"/>
       <c r="F28" t="s">
@@ -6156,7 +6150,7 @@
         <v>294</v>
       </c>
       <c r="D29" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E29"/>
       <c r="F29" t="s">
@@ -6175,7 +6169,7 @@
         <v>296</v>
       </c>
       <c r="D30" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E30"/>
       <c r="F30" t="s">
@@ -6194,7 +6188,7 @@
         <v>298</v>
       </c>
       <c r="D31" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E31"/>
       <c r="F31" t="s">
@@ -6213,7 +6207,7 @@
         <v>300</v>
       </c>
       <c r="D32" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E32"/>
       <c r="F32" t="s">
@@ -6226,7 +6220,7 @@
         <v>301</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C33" t="s">
         <v>302</v>
@@ -6272,7 +6266,7 @@
         <v>309</v>
       </c>
       <c r="D35" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E35"/>
       <c r="F35" t="s">
@@ -6314,7 +6308,7 @@
         <v>314</v>
       </c>
       <c r="D37" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E37"/>
       <c r="F37" t="s">
@@ -6333,7 +6327,7 @@
         <v>317</v>
       </c>
       <c r="D38" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E38"/>
       <c r="F38" t="s">
@@ -6392,7 +6386,7 @@
         <v>328</v>
       </c>
       <c r="D41" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E41"/>
       <c r="F41" t="s">
@@ -6434,7 +6428,7 @@
         <v>333</v>
       </c>
       <c r="D43" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E43"/>
       <c r="F43" t="s">
@@ -6554,7 +6548,7 @@
         <v>352</v>
       </c>
       <c r="D49" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E49"/>
       <c r="F49" t="s">
@@ -6592,7 +6586,7 @@
         <v>357</v>
       </c>
       <c r="D51" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E51"/>
       <c r="F51" t="s">
@@ -6611,7 +6605,7 @@
         <v>360</v>
       </c>
       <c r="D52" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E52"/>
       <c r="F52" t="s">
@@ -6651,7 +6645,7 @@
         <v>366</v>
       </c>
       <c r="D54" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E54"/>
       <c r="F54" t="s">
@@ -6672,7 +6666,7 @@
         <v>368</v>
       </c>
       <c r="D55" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E55"/>
       <c r="F55" t="s">
@@ -6697,7 +6691,7 @@
       </c>
       <c r="E56"/>
       <c r="F56" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G56"/>
     </row>
@@ -6712,7 +6706,7 @@
         <v>372</v>
       </c>
       <c r="D57" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E57"/>
       <c r="F57" t="s">
@@ -6731,7 +6725,7 @@
         <v>374</v>
       </c>
       <c r="D58" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E58"/>
       <c r="F58" t="s">
@@ -6750,7 +6744,7 @@
         <v>376</v>
       </c>
       <c r="D59" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E59"/>
       <c r="F59" t="s">
@@ -6769,7 +6763,7 @@
         <v>378</v>
       </c>
       <c r="D60" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E60"/>
       <c r="F60" t="s">
@@ -6788,7 +6782,7 @@
         <v>381</v>
       </c>
       <c r="D61" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E61"/>
       <c r="F61" t="s">
@@ -6807,7 +6801,7 @@
         <v>383</v>
       </c>
       <c r="D62" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E62"/>
       <c r="F62" t="s">
@@ -6826,7 +6820,7 @@
         <v>386</v>
       </c>
       <c r="D63" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E63"/>
       <c r="F63" t="s">
@@ -6845,7 +6839,7 @@
         <v>388</v>
       </c>
       <c r="D64" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E64"/>
       <c r="F64" t="s">
@@ -6864,7 +6858,7 @@
         <v>390</v>
       </c>
       <c r="D65" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E65"/>
       <c r="F65" t="s">
@@ -6883,7 +6877,7 @@
         <v>392</v>
       </c>
       <c r="D66" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E66"/>
       <c r="F66" t="s">
@@ -6902,7 +6896,7 @@
         <v>394</v>
       </c>
       <c r="D67" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E67"/>
       <c r="F67" t="s">
@@ -6921,7 +6915,7 @@
         <v>396</v>
       </c>
       <c r="D68" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E68"/>
       <c r="F68" t="s">
@@ -6940,7 +6934,7 @@
         <v>398</v>
       </c>
       <c r="D69" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E69"/>
       <c r="F69" t="s">
@@ -6959,7 +6953,7 @@
         <v>400</v>
       </c>
       <c r="D70" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E70"/>
       <c r="F70" t="s">
@@ -6978,7 +6972,7 @@
         <v>402</v>
       </c>
       <c r="D71" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E71"/>
       <c r="F71" t="s">
@@ -6997,7 +6991,7 @@
         <v>404</v>
       </c>
       <c r="D72" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E72"/>
       <c r="F72" t="s">
@@ -7016,7 +7010,7 @@
         <v>406</v>
       </c>
       <c r="D73" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E73"/>
       <c r="F73" t="s">
@@ -7035,7 +7029,7 @@
         <v>408</v>
       </c>
       <c r="D74" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E74"/>
       <c r="F74" t="s">
@@ -7054,7 +7048,7 @@
         <v>408</v>
       </c>
       <c r="D75" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E75"/>
       <c r="F75" t="s">
@@ -7073,7 +7067,7 @@
         <v>408</v>
       </c>
       <c r="D76" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E76"/>
       <c r="F76" t="s">
@@ -7092,7 +7086,7 @@
         <v>408</v>
       </c>
       <c r="D77" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E77"/>
       <c r="F77" t="s">
@@ -7105,13 +7099,13 @@
         <v>412</v>
       </c>
       <c r="B78" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C78" t="s">
         <v>413</v>
       </c>
       <c r="D78" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E78"/>
       <c r="F78" t="s">
@@ -7130,7 +7124,7 @@
         <v>415</v>
       </c>
       <c r="D79" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E79"/>
       <c r="F79" t="s">
@@ -7149,7 +7143,7 @@
         <v>417</v>
       </c>
       <c r="D80" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E80"/>
       <c r="F80" t="s">
@@ -7168,7 +7162,7 @@
         <v>419</v>
       </c>
       <c r="D81" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E81"/>
       <c r="F81" t="s">
@@ -7187,7 +7181,7 @@
         <v>421</v>
       </c>
       <c r="D82" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E82"/>
       <c r="F82" t="s">
@@ -7208,7 +7202,7 @@
         <v>423</v>
       </c>
       <c r="D83" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E83"/>
       <c r="F83" t="s">
@@ -7229,7 +7223,7 @@
         <v>426</v>
       </c>
       <c r="D84" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E84"/>
       <c r="F84" t="s">
@@ -7248,7 +7242,7 @@
         <v>428</v>
       </c>
       <c r="D85" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E85"/>
       <c r="F85" t="s">
@@ -7267,7 +7261,7 @@
         <v>430</v>
       </c>
       <c r="D86" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E86"/>
       <c r="F86" t="s">
@@ -7286,7 +7280,7 @@
         <v>432</v>
       </c>
       <c r="D87" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E87"/>
       <c r="F87" t="s">
@@ -7301,13 +7295,13 @@
         <v>434</v>
       </c>
       <c r="B88" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C88" t="s">
         <v>302</v>
       </c>
       <c r="D88" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E88"/>
       <c r="F88" t="s">
@@ -7322,13 +7316,13 @@
         <v>435</v>
       </c>
       <c r="B89" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C89" t="s">
         <v>436</v>
       </c>
       <c r="D89" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E89"/>
       <c r="F89" t="s">
@@ -7341,13 +7335,13 @@
         <v>437</v>
       </c>
       <c r="B90" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C90" t="s">
         <v>438</v>
       </c>
       <c r="D90" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E90"/>
       <c r="F90" t="s">
@@ -7463,7 +7457,7 @@
         <v>450</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="s">
@@ -7480,7 +7474,7 @@
         <v>452</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
@@ -7497,7 +7491,7 @@
         <v>454</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
@@ -7516,7 +7510,7 @@
         <v>456</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
@@ -7535,7 +7529,7 @@
         <v>459</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E9"/>
       <c r="F9" t="s">
@@ -7554,7 +7548,7 @@
         <v>462</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
@@ -7573,7 +7567,7 @@
         <v>465</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
@@ -7592,11 +7586,11 @@
         <v>468</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G12"/>
     </row>
@@ -7611,11 +7605,11 @@
         <v>470</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E13"/>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G13"/>
     </row>
@@ -7630,11 +7624,11 @@
         <v>472</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E14"/>
       <c r="F14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G14"/>
     </row>
@@ -7649,7 +7643,7 @@
         <v>474</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E15"/>
       <c r="F15" t="s">
@@ -7668,7 +7662,7 @@
         <v>476</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
@@ -7687,7 +7681,7 @@
         <v>478</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
@@ -7700,13 +7694,13 @@
         <v>479</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C18" t="s">
         <v>480</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E18"/>
       <c r="F18" t="s">
@@ -7719,13 +7713,13 @@
         <v>481</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
         <v>482</v>
       </c>
       <c r="D19" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E19"/>
       <c r="F19" t="s">
@@ -7738,13 +7732,13 @@
         <v>483</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C20" t="s">
         <v>484</v>
       </c>
       <c r="D20" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E20"/>
       <c r="F20" t="s">
@@ -7763,7 +7757,7 @@
         <v>486</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E21"/>
       <c r="F21" t="s">
@@ -7782,7 +7776,7 @@
         <v>488</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E22"/>
       <c r="F22" t="s">
@@ -7795,13 +7789,13 @@
         <v>489</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C23" t="s">
         <v>490</v>
       </c>
       <c r="D23" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E23"/>
       <c r="F23" t="s">
@@ -7947,7 +7941,7 @@
         <v>515</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C31" t="s">
         <v>516</v>
@@ -7985,7 +7979,7 @@
         <v>523</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C33" t="s">
         <v>524</v>
@@ -8023,7 +8017,7 @@
         <v>529</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C35" t="s">
         <v>530</v>
@@ -8080,13 +8074,13 @@
         <v>538</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C38" t="s">
         <v>539</v>
       </c>
       <c r="D38" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E38"/>
       <c r="F38" t="s">
@@ -8099,13 +8093,13 @@
         <v>540</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C39" t="s">
         <v>541</v>
       </c>
       <c r="D39" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E39"/>
       <c r="F39" t="s">
@@ -8124,7 +8118,7 @@
         <v>544</v>
       </c>
       <c r="D40" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E40"/>
       <c r="F40" t="s">
@@ -8179,13 +8173,13 @@
         <v>545</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
         <v>546</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -8197,16 +8191,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -8218,16 +8212,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
@@ -8237,16 +8231,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="s">
@@ -8256,16 +8250,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
@@ -8275,16 +8269,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C7" t="s">
         <v>547</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -8305,7 +8299,7 @@
         <v>550</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -8320,13 +8314,13 @@
         <v>551</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
         <v>552</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E9"/>
       <c r="F9" t="s">
@@ -8339,13 +8333,13 @@
         <v>553</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
         <v>554</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
@@ -8383,7 +8377,7 @@
         <v>561</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
@@ -8402,7 +8396,7 @@
         <v>564</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E13"/>
       <c r="F13" t="s">
@@ -8421,83 +8415,83 @@
         <v>567</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>568</v>
       </c>
       <c r="E14"/>
       <c r="F14" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E15"/>
       <c r="F15" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C17" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E18"/>
       <c r="F18" t="s">
@@ -8507,16 +8501,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B19" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C19" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D19" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E19"/>
       <c r="F19" t="s">
@@ -8526,16 +8520,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B20" t="s">
         <v>549</v>
       </c>
       <c r="C20" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D20" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E20"/>
       <c r="F20" t="s">
@@ -8545,16 +8539,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C21" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E21"/>
       <c r="F21" t="s">
@@ -8606,16 +8600,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -8627,16 +8621,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
@@ -8646,16 +8640,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D4" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -8667,16 +8661,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C5" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -8688,16 +8682,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B6" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C6" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D6" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -8709,16 +8703,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D7" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
@@ -8728,16 +8722,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="B8" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="C8" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
@@ -8747,16 +8741,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E9"/>
       <c r="F9" t="s">
@@ -8766,16 +8760,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
@@ -8785,16 +8779,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
@@ -8846,16 +8840,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B2" t="s">
         <v>549</v>
       </c>
       <c r="C2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -8867,16 +8861,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
@@ -8886,16 +8880,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
@@ -8905,16 +8899,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D5" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -8929,13 +8923,13 @@
         <v>545</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -8947,16 +8941,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -8968,16 +8962,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
@@ -8987,16 +8981,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E9"/>
       <c r="F9" t="s">
@@ -9006,16 +9000,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
@@ -9025,16 +9019,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B11" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C11" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -9046,16 +9040,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
@@ -9065,16 +9059,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B13" t="s">
         <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
@@ -9086,16 +9080,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E14"/>
       <c r="F14" t="s">
@@ -9105,16 +9099,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E15"/>
       <c r="F15" t="s">
@@ -9124,16 +9118,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
@@ -9143,16 +9137,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
@@ -9162,16 +9156,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B18" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C18" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E18"/>
       <c r="F18" t="s">
@@ -9181,16 +9175,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D19" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E19"/>
       <c r="F19" t="s">
@@ -9200,16 +9194,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D20" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E20"/>
       <c r="F20" t="s">
@@ -9219,16 +9213,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B21" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C21" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E21"/>
       <c r="F21" t="s">
@@ -9238,16 +9232,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B22" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C22" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E22"/>
       <c r="F22" t="s">
@@ -9257,16 +9251,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B23" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E23"/>
       <c r="F23" t="s">
@@ -9276,16 +9270,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B24" t="s">
         <v>212</v>
       </c>
       <c r="C24" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E24"/>
       <c r="F24" t="s">
@@ -9295,16 +9289,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B25" t="s">
         <v>212</v>
       </c>
       <c r="C25" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D25" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E25"/>
       <c r="F25" t="s">

--- a/sormas-base/doc/SormasDictionary.xlsx
+++ b/sormas-base/doc/SormasDictionary.xlsx
@@ -2232,14 +2232,318 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Person" displayName="Person" ref="A1:G31">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Values"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Sample_test" displayName="Sample_test" ref="A1:G12">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Values"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium10" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Task" displayName="Task" ref="A1:G19">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Values"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium11" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Facility" displayName="Facility" ref="A1:G10">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Values"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium12" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="User" displayName="User" ref="A1:G14">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Values"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium13" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Region" displayName="Region" ref="A1:G5">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Values"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="District" displayName="District" ref="A1:G6">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Values"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Community" displayName="Community" ref="A1:G3">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Values"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Location" displayName="Location" ref="A1:G10">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Values"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Case" displayName="Case" ref="A1:G38">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Values"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="CaseHospitalization" displayName="CaseHospitalization" ref="A1:G8">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Values"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Symptoms" displayName="Symptoms" ref="A1:G90">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Values"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium5" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Epidemiological_data" displayName="Epidemiological_data" ref="A1:G40">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Values"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Contact" displayName="Contact" ref="A1:G21">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Values"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Visit" displayName="Visit" ref="A1:G11">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Values"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium8" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Sample" displayName="Sample" ref="A1:G25">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Values"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -2279,19 +2583,19 @@
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G2" t="b">
@@ -2302,19 +2606,19 @@
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G3" t="b">
@@ -2325,17 +2629,17 @@
       <c r="A4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E4"/>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G4"/>
@@ -2344,17 +2648,17 @@
       <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E5"/>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G5"/>
@@ -2363,17 +2667,17 @@
       <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E6"/>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G6" t="b">
@@ -2384,17 +2688,17 @@
       <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E7"/>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G7" t="b">
@@ -2405,17 +2709,17 @@
       <c r="A8" t="s">
         <v>26</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E8"/>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G8" t="b">
@@ -2426,17 +2730,17 @@
       <c r="A9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E9"/>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G9" t="b">
@@ -2447,17 +2751,17 @@
       <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C10" t="s">
         <v>29</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E10"/>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G10" t="b">
@@ -2468,17 +2772,17 @@
       <c r="A11" t="s">
         <v>31</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
         <v>33</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E11"/>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G11" t="b">
@@ -2489,17 +2793,17 @@
       <c r="A12" t="s">
         <v>34</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C12" t="s">
         <v>36</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E12"/>
-      <c r="F12" t="s">
+      <c r="F12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G12" t="b">
@@ -2510,17 +2814,17 @@
       <c r="A13" t="s">
         <v>38</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C13" t="s">
         <v>40</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E13"/>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G13"/>
@@ -2529,17 +2833,17 @@
       <c r="A14" t="s">
         <v>42</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C14" t="s">
         <v>44</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E14"/>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G14"/>
@@ -2548,17 +2852,17 @@
       <c r="A15" t="s">
         <v>45</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C15" t="s">
         <v>47</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E15"/>
-      <c r="F15" t="s">
+      <c r="F15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G15"/>
@@ -2567,17 +2871,17 @@
       <c r="A16" t="s">
         <v>48</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
         <v>49</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E16"/>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G16"/>
@@ -2586,17 +2890,17 @@
       <c r="A17" t="s">
         <v>50</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C17" t="s">
         <v>52</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E17"/>
-      <c r="F17" t="s">
+      <c r="F17" s="1" t="s">
         <v>53</v>
       </c>
       <c r="G17"/>
@@ -2605,17 +2909,17 @@
       <c r="A18" t="s">
         <v>54</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C18" t="s">
         <v>55</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E18"/>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>53</v>
       </c>
       <c r="G18"/>
@@ -2624,17 +2928,17 @@
       <c r="A19" t="s">
         <v>56</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
         <v>57</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E19"/>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
         <v>53</v>
       </c>
       <c r="G19"/>
@@ -2643,17 +2947,17 @@
       <c r="A20" t="s">
         <v>58</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
         <v>59</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E20"/>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
         <v>53</v>
       </c>
       <c r="G20"/>
@@ -2662,17 +2966,17 @@
       <c r="A21" t="s">
         <v>60</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C21" t="s">
         <v>62</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E21"/>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>53</v>
       </c>
       <c r="G21"/>
@@ -2681,17 +2985,17 @@
       <c r="A22" t="s">
         <v>63</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C22" t="s">
         <v>64</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E22"/>
-      <c r="F22" t="s">
+      <c r="F22" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G22"/>
@@ -2700,17 +3004,17 @@
       <c r="A23" t="s">
         <v>66</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C23" t="s">
         <v>67</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E23"/>
-      <c r="F23" t="s">
+      <c r="F23" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G23"/>
@@ -2719,17 +3023,17 @@
       <c r="A24" t="s">
         <v>68</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C24" t="s">
         <v>70</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E24"/>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G24"/>
@@ -2738,17 +3042,17 @@
       <c r="A25" t="s">
         <v>71</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C25" t="s">
         <v>73</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E25"/>
-      <c r="F25" t="s">
+      <c r="F25" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G25"/>
@@ -2757,17 +3061,17 @@
       <c r="A26" t="s">
         <v>74</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C26" t="s">
         <v>75</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E26"/>
-      <c r="F26" t="s">
+      <c r="F26" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G26"/>
@@ -2776,17 +3080,17 @@
       <c r="A27" t="s">
         <v>76</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>77</v>
       </c>
       <c r="C27" t="s">
         <v>78</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E27"/>
-      <c r="F27" t="s">
+      <c r="F27" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G27"/>
@@ -2795,17 +3099,17 @@
       <c r="A28" t="s">
         <v>79</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C28" t="s">
         <v>81</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E28"/>
-      <c r="F28" t="s">
+      <c r="F28" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G28"/>
@@ -2814,17 +3118,17 @@
       <c r="A29" t="s">
         <v>82</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C29" t="s">
         <v>84</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E29"/>
-      <c r="F29" t="s">
+      <c r="F29" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G29"/>
@@ -2833,17 +3137,17 @@
       <c r="A30" t="s">
         <v>85</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C30" t="s">
         <v>87</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E30"/>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G30"/>
@@ -2852,28 +3156,31 @@
       <c r="A31" t="s">
         <v>88</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C31" t="s">
         <v>89</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E31"/>
-      <c r="F31" t="s">
+      <c r="F31" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G31"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -2913,19 +3220,19 @@
       <c r="A2" t="s">
         <v>642</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="10" t="s">
         <v>637</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="10" t="s">
         <v>11</v>
       </c>
       <c r="G2"/>
@@ -2934,19 +3241,19 @@
       <c r="A3" t="s">
         <v>643</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="10" t="s">
         <v>634</v>
       </c>
       <c r="C3" t="s">
         <v>644</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="10" t="s">
         <v>11</v>
       </c>
       <c r="G3"/>
@@ -2955,17 +3262,17 @@
       <c r="A4" t="s">
         <v>645</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>646</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E4"/>
-      <c r="F4" t="s">
+      <c r="F4" s="10" t="s">
         <v>11</v>
       </c>
       <c r="G4"/>
@@ -2974,19 +3281,19 @@
       <c r="A5" t="s">
         <v>647</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C5" t="s">
         <v>648</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="10" t="s">
         <v>649</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="10" t="s">
         <v>11</v>
       </c>
       <c r="G5"/>
@@ -2995,19 +3302,19 @@
       <c r="A6" t="s">
         <v>613</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="10" t="s">
         <v>86</v>
       </c>
       <c r="C6" t="s">
         <v>614</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="G6"/>
@@ -3016,17 +3323,17 @@
       <c r="A7" t="s">
         <v>615</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>616</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E7"/>
-      <c r="F7" t="s">
+      <c r="F7" s="10" t="s">
         <v>11</v>
       </c>
       <c r="G7"/>
@@ -3035,19 +3342,19 @@
       <c r="A8" t="s">
         <v>650</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="10" t="s">
         <v>131</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="10" t="s">
         <v>11</v>
       </c>
       <c r="G8"/>
@@ -3056,19 +3363,19 @@
       <c r="A9" t="s">
         <v>651</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="10" t="s">
         <v>652</v>
       </c>
       <c r="C9" t="s">
         <v>653</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="10" t="s">
         <v>11</v>
       </c>
       <c r="G9"/>
@@ -3077,19 +3384,19 @@
       <c r="A10" t="s">
         <v>654</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
         <v>655</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="10" t="s">
         <v>11</v>
       </c>
       <c r="G10"/>
@@ -3098,17 +3405,17 @@
       <c r="A11" t="s">
         <v>656</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="10" t="s">
         <v>212</v>
       </c>
       <c r="C11" t="s">
         <v>657</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E11"/>
-      <c r="F11" t="s">
+      <c r="F11" s="10" t="s">
         <v>11</v>
       </c>
       <c r="G11"/>
@@ -3117,28 +3424,31 @@
       <c r="A12" t="s">
         <v>658</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="10" t="s">
         <v>212</v>
       </c>
       <c r="C12" t="s">
         <v>659</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="10" t="s">
         <v>660</v>
       </c>
       <c r="E12"/>
-      <c r="F12" t="s">
+      <c r="F12" s="10" t="s">
         <v>11</v>
       </c>
       <c r="G12"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -3178,19 +3488,19 @@
       <c r="A2" t="s">
         <v>661</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="11" t="s">
         <v>662</v>
       </c>
       <c r="C2" t="s">
         <v>663</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G2"/>
@@ -3199,17 +3509,17 @@
       <c r="A3" t="s">
         <v>548</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="11" t="s">
         <v>549</v>
       </c>
       <c r="C3" t="s">
         <v>600</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E3"/>
-      <c r="F3" t="s">
+      <c r="F3" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G3"/>
@@ -3218,17 +3528,17 @@
       <c r="A4" t="s">
         <v>664</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="11" t="s">
         <v>665</v>
       </c>
       <c r="C4" t="s">
         <v>666</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E4"/>
-      <c r="F4" t="s">
+      <c r="F4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G4"/>
@@ -3237,17 +3547,17 @@
       <c r="A5" t="s">
         <v>667</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="11" t="s">
         <v>668</v>
       </c>
       <c r="C5" t="s">
         <v>669</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E5"/>
-      <c r="F5" t="s">
+      <c r="F5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G5"/>
@@ -3256,19 +3566,19 @@
       <c r="A6" t="s">
         <v>670</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="11" t="s">
         <v>671</v>
       </c>
       <c r="C6" t="s">
         <v>672</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="11" t="s">
         <v>673</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G6"/>
@@ -3277,17 +3587,17 @@
       <c r="A7" t="s">
         <v>674</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="11" t="s">
         <v>675</v>
       </c>
       <c r="C7" t="s">
         <v>676</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E7"/>
-      <c r="F7" t="s">
+      <c r="F7" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G7"/>
@@ -3296,19 +3606,19 @@
       <c r="A8" t="s">
         <v>677</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C8" t="s">
         <v>678</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G8"/>
@@ -3317,17 +3627,17 @@
       <c r="A9" t="s">
         <v>679</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C9" t="s">
         <v>680</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E9"/>
-      <c r="F9" t="s">
+      <c r="F9" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G9"/>
@@ -3336,17 +3646,17 @@
       <c r="A10" t="s">
         <v>681</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="11" t="s">
         <v>682</v>
       </c>
       <c r="C10" t="s">
         <v>683</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E10"/>
-      <c r="F10" t="s">
+      <c r="F10" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G10"/>
@@ -3355,17 +3665,17 @@
       <c r="A11" t="s">
         <v>684</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C11" t="s">
         <v>685</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E11"/>
-      <c r="F11" t="s">
+      <c r="F11" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G11"/>
@@ -3374,17 +3684,17 @@
       <c r="A12" t="s">
         <v>686</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C12" t="s">
         <v>687</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E12"/>
-      <c r="F12" t="s">
+      <c r="F12" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G12"/>
@@ -3393,17 +3703,17 @@
       <c r="A13" t="s">
         <v>688</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C13" t="s">
         <v>689</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E13"/>
-      <c r="F13" t="s">
+      <c r="F13" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G13"/>
@@ -3412,17 +3722,17 @@
       <c r="A14" t="s">
         <v>690</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
         <v>691</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E14"/>
-      <c r="F14" t="s">
+      <c r="F14" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G14"/>
@@ -3431,19 +3741,19 @@
       <c r="A15" t="s">
         <v>692</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C15" t="s">
         <v>693</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G15"/>
@@ -3452,17 +3762,17 @@
       <c r="A16" t="s">
         <v>694</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
         <v>695</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E16"/>
-      <c r="F16" t="s">
+      <c r="F16" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G16"/>
@@ -3471,17 +3781,17 @@
       <c r="A17" t="s">
         <v>696</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C17" t="s">
         <v>17</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E17"/>
-      <c r="F17" t="s">
+      <c r="F17" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G17"/>
@@ -3490,17 +3800,17 @@
       <c r="A18" t="s">
         <v>697</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C18" t="s">
         <v>17</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E18"/>
-      <c r="F18" t="s">
+      <c r="F18" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G18"/>
@@ -3509,28 +3819,31 @@
       <c r="A19" t="s">
         <v>698</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C19" t="s">
         <v>17</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E19"/>
-      <c r="F19" t="s">
+      <c r="F19" s="11" t="s">
         <v>11</v>
       </c>
       <c r="G19"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -3570,17 +3883,17 @@
       <c r="A2" t="s">
         <v>699</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>700</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E2"/>
-      <c r="F2" t="s">
+      <c r="F2" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G2"/>
@@ -3589,17 +3902,17 @@
       <c r="A3" t="s">
         <v>90</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="12" t="s">
         <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E3"/>
-      <c r="F3" t="s">
+      <c r="F3" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G3"/>
@@ -3608,17 +3921,17 @@
       <c r="A4" t="s">
         <v>92</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C4" t="s">
         <v>93</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E4"/>
-      <c r="F4" t="s">
+      <c r="F4" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G4"/>
@@ -3627,17 +3940,17 @@
       <c r="A5" t="s">
         <v>94</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="12" t="s">
         <v>83</v>
       </c>
       <c r="C5" t="s">
         <v>95</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E5"/>
-      <c r="F5" t="s">
+      <c r="F5" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G5"/>
@@ -3646,17 +3959,17 @@
       <c r="A6" t="s">
         <v>99</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
         <v>100</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E6"/>
-      <c r="F6" t="s">
+      <c r="F6" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G6"/>
@@ -3665,17 +3978,17 @@
       <c r="A7" t="s">
         <v>101</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="12" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
         <v>701</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E7"/>
-      <c r="F7" t="s">
+      <c r="F7" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G7"/>
@@ -3684,17 +3997,17 @@
       <c r="A8" t="s">
         <v>104</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="12" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
         <v>702</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E8"/>
-      <c r="F8" t="s">
+      <c r="F8" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G8"/>
@@ -3703,17 +4016,17 @@
       <c r="A9" t="s">
         <v>703</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="12" t="s">
         <v>704</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E9"/>
-      <c r="F9" t="s">
+      <c r="F9" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G9"/>
@@ -3722,28 +4035,31 @@
       <c r="A10" t="s">
         <v>705</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="12" t="s">
         <v>212</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E10"/>
-      <c r="F10" t="s">
+      <c r="F10" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G10"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -3783,17 +4099,17 @@
       <c r="A2" t="s">
         <v>706</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="13" t="s">
         <v>212</v>
       </c>
       <c r="C2" t="s">
         <v>707</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E2"/>
-      <c r="F2" t="s">
+      <c r="F2" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G2"/>
@@ -3802,17 +4118,17 @@
       <c r="A3" t="s">
         <v>708</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>709</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E3"/>
-      <c r="F3" t="s">
+      <c r="F3" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G3"/>
@@ -3821,17 +4137,17 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E4"/>
-      <c r="F4" t="s">
+      <c r="F4" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G4"/>
@@ -3840,17 +4156,17 @@
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E5"/>
-      <c r="F5" t="s">
+      <c r="F5" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G5"/>
@@ -3859,17 +4175,17 @@
       <c r="A6" t="s">
         <v>710</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
         <v>711</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E6"/>
-      <c r="F6" t="s">
+      <c r="F6" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G6"/>
@@ -3878,17 +4194,17 @@
       <c r="A7" t="s">
         <v>63</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>64</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E7"/>
-      <c r="F7" t="s">
+      <c r="F7" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G7"/>
@@ -3897,17 +4213,17 @@
       <c r="A8" t="s">
         <v>68</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="13" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E8"/>
-      <c r="F8" t="s">
+      <c r="F8" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G8"/>
@@ -3916,15 +4232,15 @@
       <c r="A9" t="s">
         <v>712</v>
       </c>
-      <c r="B9"/>
+      <c r="B9" s="13"/>
       <c r="C9" t="s">
         <v>713</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E9"/>
-      <c r="F9" t="s">
+      <c r="F9" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G9"/>
@@ -3933,17 +4249,17 @@
       <c r="A10" t="s">
         <v>90</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="13" t="s">
         <v>77</v>
       </c>
       <c r="C10" t="s">
         <v>91</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E10"/>
-      <c r="F10" t="s">
+      <c r="F10" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G10"/>
@@ -3952,17 +4268,17 @@
       <c r="A11" t="s">
         <v>92</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="13" t="s">
         <v>80</v>
       </c>
       <c r="C11" t="s">
         <v>93</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E11"/>
-      <c r="F11" t="s">
+      <c r="F11" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G11"/>
@@ -3971,17 +4287,17 @@
       <c r="A12" t="s">
         <v>155</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="13" t="s">
         <v>86</v>
       </c>
       <c r="C12" t="s">
         <v>156</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E12"/>
-      <c r="F12" t="s">
+      <c r="F12" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G12"/>
@@ -3990,17 +4306,17 @@
       <c r="A13" t="s">
         <v>714</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="13" t="s">
         <v>86</v>
       </c>
       <c r="C13" t="s">
         <v>614</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E13"/>
-      <c r="F13" t="s">
+      <c r="F13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G13"/>
@@ -4009,28 +4325,31 @@
       <c r="A14" t="s">
         <v>715</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="13" t="s">
         <v>131</v>
       </c>
       <c r="C14" t="s">
         <v>716</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E14"/>
-      <c r="F14" t="s">
+      <c r="F14" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G14"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -4070,17 +4389,17 @@
       <c r="A2" t="s">
         <v>699</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>700</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E2"/>
-      <c r="F2" t="s">
+      <c r="F2" s="14" t="s">
         <v>11</v>
       </c>
       <c r="G2"/>
@@ -4089,17 +4408,17 @@
       <c r="A3" t="s">
         <v>717</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>718</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E3"/>
-      <c r="F3" t="s">
+      <c r="F3" s="14" t="s">
         <v>11</v>
       </c>
       <c r="G3"/>
@@ -4108,17 +4427,17 @@
       <c r="A4" t="s">
         <v>719</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
         <v>720</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E4"/>
-      <c r="F4" t="s">
+      <c r="F4" s="14" t="s">
         <v>11</v>
       </c>
       <c r="G4"/>
@@ -4127,28 +4446,31 @@
       <c r="A5" t="s">
         <v>721</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>722</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E5"/>
-      <c r="F5" t="s">
+      <c r="F5" s="14" t="s">
         <v>11</v>
       </c>
       <c r="G5"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -4188,17 +4510,17 @@
       <c r="A2" t="s">
         <v>699</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>700</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="15" t="s">
         <v>17</v>
       </c>
       <c r="E2"/>
-      <c r="F2" t="s">
+      <c r="F2" s="15" t="s">
         <v>11</v>
       </c>
       <c r="G2"/>
@@ -4207,17 +4529,17 @@
       <c r="A3" t="s">
         <v>717</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>718</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="15" t="s">
         <v>17</v>
       </c>
       <c r="E3"/>
-      <c r="F3" t="s">
+      <c r="F3" s="15" t="s">
         <v>11</v>
       </c>
       <c r="G3"/>
@@ -4226,17 +4548,17 @@
       <c r="A4" t="s">
         <v>719</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
         <v>720</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="15" t="s">
         <v>17</v>
       </c>
       <c r="E4"/>
-      <c r="F4" t="s">
+      <c r="F4" s="15" t="s">
         <v>11</v>
       </c>
       <c r="G4"/>
@@ -4245,17 +4567,17 @@
       <c r="A5" t="s">
         <v>721</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>722</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="15" t="s">
         <v>17</v>
       </c>
       <c r="E5"/>
-      <c r="F5" t="s">
+      <c r="F5" s="15" t="s">
         <v>11</v>
       </c>
       <c r="G5"/>
@@ -4264,28 +4586,31 @@
       <c r="A6" t="s">
         <v>90</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="15" t="s">
         <v>77</v>
       </c>
       <c r="C6" t="s">
         <v>91</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="15" t="s">
         <v>17</v>
       </c>
       <c r="E6"/>
-      <c r="F6" t="s">
+      <c r="F6" s="15" t="s">
         <v>11</v>
       </c>
       <c r="G6"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -4325,17 +4650,17 @@
       <c r="A2" t="s">
         <v>699</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="16" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>700</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="16" t="s">
         <v>17</v>
       </c>
       <c r="E2"/>
-      <c r="F2" t="s">
+      <c r="F2" s="16" t="s">
         <v>11</v>
       </c>
       <c r="G2"/>
@@ -4344,28 +4669,31 @@
       <c r="A3" t="s">
         <v>92</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="16" t="s">
         <v>80</v>
       </c>
       <c r="C3" t="s">
         <v>93</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="16" t="s">
         <v>17</v>
       </c>
       <c r="E3"/>
-      <c r="F3" t="s">
+      <c r="F3" s="16" t="s">
         <v>11</v>
       </c>
       <c r="G3"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -4405,17 +4733,17 @@
       <c r="A2" t="s">
         <v>90</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C2" t="s">
         <v>91</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E2"/>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G2"/>
@@ -4424,17 +4752,17 @@
       <c r="A3" t="s">
         <v>92</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C3" t="s">
         <v>93</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E3"/>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G3"/>
@@ -4443,17 +4771,17 @@
       <c r="A4" t="s">
         <v>94</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C4" t="s">
         <v>95</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E4"/>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G4"/>
@@ -4462,17 +4790,17 @@
       <c r="A5" t="s">
         <v>68</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>96</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E5"/>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G5"/>
@@ -4481,17 +4809,17 @@
       <c r="A6" t="s">
         <v>97</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
         <v>98</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E6"/>
-      <c r="F6" t="s">
+      <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G6"/>
@@ -4500,17 +4828,17 @@
       <c r="A7" t="s">
         <v>99</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>100</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E7"/>
-      <c r="F7" t="s">
+      <c r="F7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G7"/>
@@ -4519,17 +4847,17 @@
       <c r="A8" t="s">
         <v>101</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
         <v>102</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>103</v>
       </c>
       <c r="E8"/>
-      <c r="F8" t="s">
+      <c r="F8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G8"/>
@@ -4538,17 +4866,17 @@
       <c r="A9" t="s">
         <v>104</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
         <v>105</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>106</v>
       </c>
       <c r="E9"/>
-      <c r="F9" t="s">
+      <c r="F9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G9"/>
@@ -4557,28 +4885,31 @@
       <c r="A10" t="s">
         <v>107</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C10" t="s">
         <v>108</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>109</v>
       </c>
       <c r="E10"/>
-      <c r="F10" t="s">
+      <c r="F10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G10"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -4618,19 +4949,19 @@
       <c r="A2" t="s">
         <v>110</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C2" t="s">
         <v>111</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G2" t="b">
@@ -4641,17 +4972,17 @@
       <c r="A3" t="s">
         <v>113</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>114</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E3"/>
-      <c r="F3" t="s">
+      <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G3" t="b">
@@ -4662,17 +4993,17 @@
       <c r="A4" t="s">
         <v>115</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>116</v>
       </c>
       <c r="C4" t="s">
         <v>117</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E4"/>
-      <c r="F4" t="s">
+      <c r="F4" s="3" t="s">
         <v>118</v>
       </c>
       <c r="G4" t="b">
@@ -4683,17 +5014,17 @@
       <c r="A5" t="s">
         <v>119</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>120</v>
       </c>
       <c r="C5" t="s">
         <v>121</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E5"/>
-      <c r="F5" t="s">
+      <c r="F5" s="3" t="s">
         <v>122</v>
       </c>
       <c r="G5" t="b">
@@ -4704,19 +5035,19 @@
       <c r="A6" t="s">
         <v>123</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>124</v>
       </c>
       <c r="C6" t="s">
         <v>125</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G6"/>
@@ -4725,17 +5056,17 @@
       <c r="A7" t="s">
         <v>126</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>127</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E7"/>
-      <c r="F7" t="s">
+      <c r="F7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G7" t="b">
@@ -4746,19 +5077,19 @@
       <c r="A8" t="s">
         <v>128</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C8" t="s">
         <v>129</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G8" t="b">
@@ -4769,19 +5100,19 @@
       <c r="A9" t="s">
         <v>130</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>131</v>
       </c>
       <c r="C9" t="s">
         <v>132</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G9" t="b">
@@ -4792,17 +5123,17 @@
       <c r="A10" t="s">
         <v>133</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C10" t="s">
         <v>134</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="3" t="s">
         <v>135</v>
       </c>
       <c r="E10"/>
-      <c r="F10" t="s">
+      <c r="F10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G10" t="b">
@@ -4813,19 +5144,19 @@
       <c r="A11" t="s">
         <v>136</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="3" t="s">
         <v>137</v>
       </c>
       <c r="C11" t="s">
         <v>138</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="3" t="s">
         <v>139</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G11" t="b">
@@ -4836,17 +5167,17 @@
       <c r="A12" t="s">
         <v>140</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>131</v>
       </c>
       <c r="C12" t="s">
         <v>141</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E12"/>
-      <c r="F12" t="s">
+      <c r="F12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G12" t="b">
@@ -4857,17 +5188,17 @@
       <c r="A13" t="s">
         <v>142</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C13" t="s">
         <v>143</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E13"/>
-      <c r="F13" t="s">
+      <c r="F13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G13" t="b">
@@ -4878,17 +5209,17 @@
       <c r="A14" t="s">
         <v>144</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
         <v>17</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E14"/>
-      <c r="F14" t="s">
+      <c r="F14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G14" t="b">
@@ -4899,19 +5230,19 @@
       <c r="A15" t="s">
         <v>145</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>146</v>
       </c>
       <c r="C15" t="s">
         <v>147</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G15" t="b">
@@ -4922,17 +5253,17 @@
       <c r="A16" t="s">
         <v>148</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C16" t="s">
         <v>149</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E16"/>
-      <c r="F16" t="s">
+      <c r="F16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G16" t="b">
@@ -4943,17 +5274,17 @@
       <c r="A17" t="s">
         <v>150</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>151</v>
       </c>
       <c r="C17" t="s">
         <v>152</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E17"/>
-      <c r="F17" t="s">
+      <c r="F17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G17" t="b">
@@ -4964,17 +5295,17 @@
       <c r="A18" t="s">
         <v>153</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C18" t="s">
         <v>154</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E18"/>
-      <c r="F18" t="s">
+      <c r="F18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G18" t="b">
@@ -4985,19 +5316,19 @@
       <c r="A19" t="s">
         <v>90</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="3" t="s">
         <v>77</v>
       </c>
       <c r="C19" t="s">
         <v>91</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G19" t="b">
@@ -5008,19 +5339,19 @@
       <c r="A20" t="s">
         <v>92</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C20" t="s">
         <v>93</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G20" t="b">
@@ -5031,17 +5362,17 @@
       <c r="A21" t="s">
         <v>94</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="3" t="s">
         <v>83</v>
       </c>
       <c r="C21" t="s">
         <v>95</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E21"/>
-      <c r="F21" t="s">
+      <c r="F21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G21" t="b">
@@ -5052,19 +5383,19 @@
       <c r="A22" t="s">
         <v>155</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C22" t="s">
         <v>156</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="3" t="s">
         <v>157</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G22" t="b">
@@ -5075,17 +5406,17 @@
       <c r="A23" t="s">
         <v>158</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C23" t="s">
         <v>89</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E23"/>
-      <c r="F23" t="s">
+      <c r="F23" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G23" t="b">
@@ -5096,17 +5427,17 @@
       <c r="A24" t="s">
         <v>159</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="3" t="s">
         <v>160</v>
       </c>
       <c r="C24" t="s">
         <v>161</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="3" t="s">
         <v>162</v>
       </c>
       <c r="E24"/>
-      <c r="F24" t="s">
+      <c r="F24" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G24"/>
@@ -5115,17 +5446,17 @@
       <c r="A25" t="s">
         <v>163</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="3" t="s">
         <v>164</v>
       </c>
       <c r="C25" t="s">
         <v>165</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E25"/>
-      <c r="F25" t="s">
+      <c r="F25" s="3" t="s">
         <v>166</v>
       </c>
       <c r="G25" t="b">
@@ -5136,17 +5467,17 @@
       <c r="A26" t="s">
         <v>167</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C26" t="s">
         <v>168</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E26"/>
-      <c r="F26" t="s">
+      <c r="F26" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G26" t="b">
@@ -5157,17 +5488,17 @@
       <c r="A27" t="s">
         <v>170</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C27" t="s">
         <v>171</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E27"/>
-      <c r="F27" t="s">
+      <c r="F27" s="3" t="s">
         <v>172</v>
       </c>
       <c r="G27" t="b">
@@ -5178,17 +5509,17 @@
       <c r="A28" t="s">
         <v>173</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="3" t="s">
         <v>174</v>
       </c>
       <c r="C28" t="s">
         <v>175</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E28"/>
-      <c r="F28" t="s">
+      <c r="F28" s="3" t="s">
         <v>166</v>
       </c>
       <c r="G28"/>
@@ -5197,17 +5528,17 @@
       <c r="A29" t="s">
         <v>176</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="3" t="s">
         <v>160</v>
       </c>
       <c r="C29" t="s">
         <v>177</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E29"/>
-      <c r="F29" t="s">
+      <c r="F29" s="3" t="s">
         <v>178</v>
       </c>
       <c r="G29"/>
@@ -5216,17 +5547,17 @@
       <c r="A30" t="s">
         <v>179</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="3" t="s">
         <v>160</v>
       </c>
       <c r="C30" t="s">
         <v>180</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E30"/>
-      <c r="F30" t="s">
+      <c r="F30" s="3" t="s">
         <v>178</v>
       </c>
       <c r="G30"/>
@@ -5235,17 +5566,17 @@
       <c r="A31" t="s">
         <v>181</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="3" t="s">
         <v>131</v>
       </c>
       <c r="C31" t="s">
         <v>182</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E31"/>
-      <c r="F31" t="s">
+      <c r="F31" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G31" t="b">
@@ -5256,17 +5587,17 @@
       <c r="A32" t="s">
         <v>183</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="3" t="s">
         <v>131</v>
       </c>
       <c r="C32" t="s">
         <v>184</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E32"/>
-      <c r="F32" t="s">
+      <c r="F32" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G32"/>
@@ -5275,17 +5606,17 @@
       <c r="A33" t="s">
         <v>185</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C33" t="s">
         <v>17</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E33"/>
-      <c r="F33" t="s">
+      <c r="F33" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G33"/>
@@ -5294,17 +5625,17 @@
       <c r="A34" t="s">
         <v>186</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C34" t="s">
         <v>17</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E34"/>
-      <c r="F34" t="s">
+      <c r="F34" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G34"/>
@@ -5313,17 +5644,17 @@
       <c r="A35" t="s">
         <v>187</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C35" t="s">
         <v>17</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E35"/>
-      <c r="F35" t="s">
+      <c r="F35" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G35"/>
@@ -5332,17 +5663,17 @@
       <c r="A36" t="s">
         <v>188</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="3" t="s">
         <v>189</v>
       </c>
       <c r="C36" t="s">
         <v>189</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E36"/>
-      <c r="F36" t="s">
+      <c r="F36" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G36"/>
@@ -5351,17 +5682,17 @@
       <c r="A37" t="s">
         <v>190</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="3" t="s">
         <v>191</v>
       </c>
       <c r="C37" t="s">
         <v>191</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E37"/>
-      <c r="F37" t="s">
+      <c r="F37" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G37"/>
@@ -5370,28 +5701,31 @@
       <c r="A38" t="s">
         <v>192</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="3" t="s">
         <v>193</v>
       </c>
       <c r="C38" t="s">
         <v>194</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E38"/>
-      <c r="F38" t="s">
+      <c r="F38" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G38"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -5431,17 +5765,17 @@
       <c r="A2" t="s">
         <v>195</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>160</v>
       </c>
       <c r="C2" t="s">
         <v>196</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E2"/>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G2" t="b">
@@ -5452,17 +5786,17 @@
       <c r="A3" t="s">
         <v>197</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C3" t="s">
         <v>198</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>199</v>
       </c>
       <c r="E3"/>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G3"/>
@@ -5471,17 +5805,17 @@
       <c r="A4" t="s">
         <v>200</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C4" t="s">
         <v>201</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E4"/>
-      <c r="F4" t="s">
+      <c r="F4" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G4"/>
@@ -5490,17 +5824,17 @@
       <c r="A5" t="s">
         <v>202</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>160</v>
       </c>
       <c r="C5" t="s">
         <v>203</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>204</v>
       </c>
       <c r="E5"/>
-      <c r="F5" t="s">
+      <c r="F5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G5"/>
@@ -5509,17 +5843,17 @@
       <c r="A6" t="s">
         <v>205</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C6" t="s">
         <v>206</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E6"/>
-      <c r="F6" t="s">
+      <c r="F6" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G6"/>
@@ -5528,17 +5862,17 @@
       <c r="A7" t="s">
         <v>207</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>160</v>
       </c>
       <c r="C7" t="s">
         <v>208</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E7"/>
-      <c r="F7" t="s">
+      <c r="F7" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G7"/>
@@ -5547,26 +5881,29 @@
       <c r="A8" t="s">
         <v>209</v>
       </c>
-      <c r="B8"/>
+      <c r="B8" s="4"/>
       <c r="C8" t="s">
         <v>210</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E8"/>
-      <c r="F8" t="s">
+      <c r="F8" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G8"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -5606,17 +5943,17 @@
       <c r="A2" t="s">
         <v>211</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5" t="s">
         <v>212</v>
       </c>
       <c r="C2" t="s">
         <v>213</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="5" t="s">
         <v>214</v>
       </c>
       <c r="E2"/>
-      <c r="F2" t="s">
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G2"/>
@@ -5625,17 +5962,17 @@
       <c r="A3" t="s">
         <v>215</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C3" t="s">
         <v>216</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="5" t="s">
         <v>217</v>
       </c>
       <c r="E3"/>
-      <c r="F3" t="s">
+      <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G3" t="b">
@@ -5646,17 +5983,17 @@
       <c r="A4" t="s">
         <v>218</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>219</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="5" t="s">
         <v>220</v>
       </c>
       <c r="E4"/>
-      <c r="F4" t="s">
+      <c r="F4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G4"/>
@@ -5665,17 +6002,17 @@
       <c r="A5" t="s">
         <v>221</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>222</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="5" t="s">
         <v>223</v>
       </c>
       <c r="E5"/>
-      <c r="F5" t="s">
+      <c r="F5" s="5" t="s">
         <v>224</v>
       </c>
       <c r="G5" t="b">
@@ -5686,17 +6023,17 @@
       <c r="A6" t="s">
         <v>225</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>226</v>
       </c>
       <c r="C6" t="s">
         <v>227</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="5" t="s">
         <v>228</v>
       </c>
       <c r="E6"/>
-      <c r="F6" t="s">
+      <c r="F6" s="5" t="s">
         <v>224</v>
       </c>
       <c r="G6" t="b">
@@ -5707,17 +6044,17 @@
       <c r="A7" t="s">
         <v>229</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C7" t="s">
         <v>230</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="5" t="s">
         <v>231</v>
       </c>
       <c r="E7"/>
-      <c r="F7" t="s">
+      <c r="F7" s="5" t="s">
         <v>224</v>
       </c>
       <c r="G7" t="b">
@@ -5728,17 +6065,17 @@
       <c r="A8" t="s">
         <v>232</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C8" t="s">
         <v>233</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E8"/>
-      <c r="F8" t="s">
+      <c r="F8" s="5" t="s">
         <v>224</v>
       </c>
       <c r="G8" t="b">
@@ -5749,17 +6086,17 @@
       <c r="A9" t="s">
         <v>234</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C9" t="s">
         <v>235</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="5" t="s">
         <v>236</v>
       </c>
       <c r="E9"/>
-      <c r="F9" t="s">
+      <c r="F9" s="5" t="s">
         <v>237</v>
       </c>
       <c r="G9" t="b">
@@ -5770,17 +6107,17 @@
       <c r="A10" t="s">
         <v>238</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C10" t="s">
         <v>239</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E10"/>
-      <c r="F10" t="s">
+      <c r="F10" s="5" t="s">
         <v>240</v>
       </c>
       <c r="G10"/>
@@ -5789,17 +6126,17 @@
       <c r="A11" t="s">
         <v>241</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C11" t="s">
         <v>242</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="5" t="s">
         <v>243</v>
       </c>
       <c r="E11"/>
-      <c r="F11" t="s">
+      <c r="F11" s="5" t="s">
         <v>244</v>
       </c>
       <c r="G11"/>
@@ -5808,17 +6145,17 @@
       <c r="A12" t="s">
         <v>245</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C12" t="s">
         <v>246</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E12"/>
-      <c r="F12" t="s">
+      <c r="F12" s="5" t="s">
         <v>240</v>
       </c>
       <c r="G12"/>
@@ -5827,17 +6164,17 @@
       <c r="A13" t="s">
         <v>247</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C13" t="s">
         <v>248</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E13"/>
-      <c r="F13" t="s">
+      <c r="F13" s="5" t="s">
         <v>249</v>
       </c>
       <c r="G13" t="b">
@@ -5848,17 +6185,17 @@
       <c r="A14" t="s">
         <v>250</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C14" t="s">
         <v>251</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E14"/>
-      <c r="F14" t="s">
+      <c r="F14" s="5" t="s">
         <v>252</v>
       </c>
       <c r="G14" t="b">
@@ -5869,17 +6206,17 @@
       <c r="A15" t="s">
         <v>253</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C15" t="s">
         <v>254</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E15"/>
-      <c r="F15" t="s">
+      <c r="F15" s="5" t="s">
         <v>255</v>
       </c>
       <c r="G15"/>
@@ -5888,17 +6225,17 @@
       <c r="A16" t="s">
         <v>256</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C16" t="s">
         <v>257</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E16"/>
-      <c r="F16" t="s">
+      <c r="F16" s="5" t="s">
         <v>258</v>
       </c>
       <c r="G16" t="b">
@@ -5909,17 +6246,17 @@
       <c r="A17" t="s">
         <v>259</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C17" t="s">
         <v>260</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="5" t="s">
         <v>261</v>
       </c>
       <c r="E17"/>
-      <c r="F17" t="s">
+      <c r="F17" s="5" t="s">
         <v>224</v>
       </c>
       <c r="G17" t="b">
@@ -5930,17 +6267,17 @@
       <c r="A18" t="s">
         <v>262</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C18" t="s">
         <v>263</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="5" t="s">
         <v>264</v>
       </c>
       <c r="E18"/>
-      <c r="F18" t="s">
+      <c r="F18" s="5" t="s">
         <v>224</v>
       </c>
       <c r="G18" t="b">
@@ -5951,17 +6288,17 @@
       <c r="A19" t="s">
         <v>265</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C19" t="s">
         <v>266</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="5" t="s">
         <v>267</v>
       </c>
       <c r="E19"/>
-      <c r="F19" t="s">
+      <c r="F19" s="5" t="s">
         <v>268</v>
       </c>
       <c r="G19"/>
@@ -5970,17 +6307,17 @@
       <c r="A20" t="s">
         <v>269</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C20" t="s">
         <v>270</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E20"/>
-      <c r="F20" t="s">
+      <c r="F20" s="5" t="s">
         <v>271</v>
       </c>
       <c r="G20"/>
@@ -5989,17 +6326,17 @@
       <c r="A21" t="s">
         <v>272</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C21" t="s">
         <v>273</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E21"/>
-      <c r="F21" t="s">
+      <c r="F21" s="5" t="s">
         <v>274</v>
       </c>
       <c r="G21"/>
@@ -6008,17 +6345,17 @@
       <c r="A22" t="s">
         <v>275</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C22" t="s">
         <v>276</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E22"/>
-      <c r="F22" t="s">
+      <c r="F22" s="5" t="s">
         <v>271</v>
       </c>
       <c r="G22"/>
@@ -6027,17 +6364,17 @@
       <c r="A23" t="s">
         <v>277</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C23" t="s">
         <v>278</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E23"/>
-      <c r="F23" t="s">
+      <c r="F23" s="5" t="s">
         <v>279</v>
       </c>
       <c r="G23"/>
@@ -6046,17 +6383,17 @@
       <c r="A24" t="s">
         <v>280</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C24" t="s">
         <v>281</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E24"/>
-      <c r="F24" t="s">
+      <c r="F24" s="5" t="s">
         <v>282</v>
       </c>
       <c r="G24"/>
@@ -6065,17 +6402,17 @@
       <c r="A25" t="s">
         <v>283</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C25" t="s">
         <v>284</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E25"/>
-      <c r="F25" t="s">
+      <c r="F25" s="5" t="s">
         <v>279</v>
       </c>
       <c r="G25"/>
@@ -6084,17 +6421,17 @@
       <c r="A26" t="s">
         <v>285</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C26" t="s">
         <v>286</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E26"/>
-      <c r="F26" t="s">
+      <c r="F26" s="5" t="s">
         <v>287</v>
       </c>
       <c r="G26"/>
@@ -6103,17 +6440,17 @@
       <c r="A27" t="s">
         <v>288</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C27" t="s">
         <v>289</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E27"/>
-      <c r="F27" t="s">
+      <c r="F27" s="5" t="s">
         <v>279</v>
       </c>
       <c r="G27"/>
@@ -6122,17 +6459,17 @@
       <c r="A28" t="s">
         <v>290</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C28" t="s">
         <v>291</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E28"/>
-      <c r="F28" t="s">
+      <c r="F28" s="5" t="s">
         <v>292</v>
       </c>
       <c r="G28" t="b">
@@ -6143,17 +6480,17 @@
       <c r="A29" t="s">
         <v>293</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C29" t="s">
         <v>294</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E29"/>
-      <c r="F29" t="s">
+      <c r="F29" s="5" t="s">
         <v>279</v>
       </c>
       <c r="G29"/>
@@ -6162,17 +6499,17 @@
       <c r="A30" t="s">
         <v>295</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C30" t="s">
         <v>296</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E30"/>
-      <c r="F30" t="s">
+      <c r="F30" s="5" t="s">
         <v>279</v>
       </c>
       <c r="G30"/>
@@ -6181,17 +6518,17 @@
       <c r="A31" t="s">
         <v>297</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C31" t="s">
         <v>298</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E31"/>
-      <c r="F31" t="s">
+      <c r="F31" s="5" t="s">
         <v>279</v>
       </c>
       <c r="G31"/>
@@ -6200,17 +6537,17 @@
       <c r="A32" t="s">
         <v>299</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C32" t="s">
         <v>300</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E32"/>
-      <c r="F32" t="s">
+      <c r="F32" s="5" t="s">
         <v>292</v>
       </c>
       <c r="G32"/>
@@ -6219,17 +6556,17 @@
       <c r="A33" t="s">
         <v>301</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" t="s">
         <v>302</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="5" t="s">
         <v>303</v>
       </c>
       <c r="E33"/>
-      <c r="F33" t="s">
+      <c r="F33" s="5" t="s">
         <v>292</v>
       </c>
       <c r="G33"/>
@@ -6238,17 +6575,17 @@
       <c r="A34" t="s">
         <v>304</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C34" t="s">
         <v>305</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="5" t="s">
         <v>306</v>
       </c>
       <c r="E34"/>
-      <c r="F34" t="s">
+      <c r="F34" s="5" t="s">
         <v>307</v>
       </c>
       <c r="G34" t="b">
@@ -6259,17 +6596,17 @@
       <c r="A35" t="s">
         <v>308</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C35" t="s">
         <v>309</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E35"/>
-      <c r="F35" t="s">
+      <c r="F35" s="5" t="s">
         <v>249</v>
       </c>
       <c r="G35" t="b">
@@ -6280,17 +6617,17 @@
       <c r="A36" t="s">
         <v>310</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C36" t="s">
         <v>311</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="5" t="s">
         <v>312</v>
       </c>
       <c r="E36"/>
-      <c r="F36" t="s">
+      <c r="F36" s="5" t="s">
         <v>249</v>
       </c>
       <c r="G36" t="b">
@@ -6301,17 +6638,17 @@
       <c r="A37" t="s">
         <v>313</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C37" t="s">
         <v>314</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E37"/>
-      <c r="F37" t="s">
+      <c r="F37" s="5" t="s">
         <v>315</v>
       </c>
       <c r="G37"/>
@@ -6320,17 +6657,17 @@
       <c r="A38" t="s">
         <v>316</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C38" t="s">
         <v>317</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E38"/>
-      <c r="F38" t="s">
+      <c r="F38" s="5" t="s">
         <v>318</v>
       </c>
       <c r="G38" t="b">
@@ -6341,17 +6678,17 @@
       <c r="A39" t="s">
         <v>319</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C39" t="s">
         <v>320</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="5" t="s">
         <v>321</v>
       </c>
       <c r="E39"/>
-      <c r="F39" t="s">
+      <c r="F39" s="5" t="s">
         <v>322</v>
       </c>
       <c r="G39"/>
@@ -6360,17 +6697,17 @@
       <c r="A40" t="s">
         <v>323</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C40" t="s">
         <v>324</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="5" t="s">
         <v>325</v>
       </c>
       <c r="E40"/>
-      <c r="F40" t="s">
+      <c r="F40" s="5" t="s">
         <v>326</v>
       </c>
       <c r="G40"/>
@@ -6379,17 +6716,17 @@
       <c r="A41" t="s">
         <v>327</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C41" t="s">
         <v>328</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E41"/>
-      <c r="F41" t="s">
+      <c r="F41" s="5" t="s">
         <v>329</v>
       </c>
       <c r="G41" t="b">
@@ -6400,17 +6737,17 @@
       <c r="A42" t="s">
         <v>330</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C42" t="s">
         <v>331</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="5" t="s">
         <v>331</v>
       </c>
       <c r="E42"/>
-      <c r="F42" t="s">
+      <c r="F42" s="5" t="s">
         <v>237</v>
       </c>
       <c r="G42" t="b">
@@ -6421,17 +6758,17 @@
       <c r="A43" t="s">
         <v>332</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C43" t="s">
         <v>333</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E43"/>
-      <c r="F43" t="s">
+      <c r="F43" s="5" t="s">
         <v>334</v>
       </c>
       <c r="G43" t="b">
@@ -6442,17 +6779,17 @@
       <c r="A44" t="s">
         <v>335</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C44" t="s">
         <v>336</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="5" t="s">
         <v>337</v>
       </c>
       <c r="E44"/>
-      <c r="F44" t="s">
+      <c r="F44" s="5" t="s">
         <v>334</v>
       </c>
       <c r="G44" t="b">
@@ -6463,17 +6800,17 @@
       <c r="A45" t="s">
         <v>338</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C45" t="s">
         <v>339</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="5" t="s">
         <v>340</v>
       </c>
       <c r="E45"/>
-      <c r="F45" t="s">
+      <c r="F45" s="5" t="s">
         <v>315</v>
       </c>
       <c r="G45"/>
@@ -6482,17 +6819,17 @@
       <c r="A46" t="s">
         <v>341</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C46" t="s">
         <v>342</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="5" t="s">
         <v>343</v>
       </c>
       <c r="E46"/>
-      <c r="F46" t="s">
+      <c r="F46" s="5" t="s">
         <v>344</v>
       </c>
       <c r="G46" t="b">
@@ -6503,17 +6840,17 @@
       <c r="A47" t="s">
         <v>345</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C47" t="s">
         <v>346</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="5" t="s">
         <v>346</v>
       </c>
       <c r="E47"/>
-      <c r="F47" t="s">
+      <c r="F47" s="5" t="s">
         <v>347</v>
       </c>
       <c r="G47"/>
@@ -6522,17 +6859,17 @@
       <c r="A48" t="s">
         <v>348</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C48" t="s">
         <v>349</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="5" t="s">
         <v>350</v>
       </c>
       <c r="E48"/>
-      <c r="F48" t="s">
+      <c r="F48" s="5" t="s">
         <v>279</v>
       </c>
       <c r="G48"/>
@@ -6541,17 +6878,17 @@
       <c r="A49" t="s">
         <v>351</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C49" t="s">
         <v>352</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E49"/>
-      <c r="F49" t="s">
+      <c r="F49" s="5" t="s">
         <v>322</v>
       </c>
       <c r="G49"/>
@@ -6560,17 +6897,17 @@
       <c r="A50" t="s">
         <v>353</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C50" t="s">
         <v>354</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="5" t="s">
         <v>355</v>
       </c>
       <c r="E50"/>
-      <c r="F50" t="s">
+      <c r="F50" s="5" t="s">
         <v>279</v>
       </c>
       <c r="G50"/>
@@ -6579,17 +6916,17 @@
       <c r="A51" t="s">
         <v>356</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C51" t="s">
         <v>357</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E51"/>
-      <c r="F51" t="s">
+      <c r="F51" s="5" t="s">
         <v>358</v>
       </c>
       <c r="G51"/>
@@ -6598,17 +6935,17 @@
       <c r="A52" t="s">
         <v>359</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C52" t="s">
         <v>360</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E52"/>
-      <c r="F52" t="s">
+      <c r="F52" s="5" t="s">
         <v>361</v>
       </c>
       <c r="G52" t="b">
@@ -6619,17 +6956,17 @@
       <c r="A53" t="s">
         <v>362</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C53" t="s">
         <v>363</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="5" t="s">
         <v>363</v>
       </c>
       <c r="E53"/>
-      <c r="F53" t="s">
+      <c r="F53" s="5" t="s">
         <v>364</v>
       </c>
       <c r="G53"/>
@@ -6638,17 +6975,17 @@
       <c r="A54" t="s">
         <v>365</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C54" t="s">
         <v>366</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E54"/>
-      <c r="F54" t="s">
+      <c r="F54" s="5" t="s">
         <v>307</v>
       </c>
       <c r="G54" t="b">
@@ -6659,17 +6996,17 @@
       <c r="A55" t="s">
         <v>367</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C55" t="s">
         <v>368</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E55"/>
-      <c r="F55" t="s">
+      <c r="F55" s="5" t="s">
         <v>237</v>
       </c>
       <c r="G55" t="b">
@@ -6680,17 +7017,17 @@
       <c r="A56" t="s">
         <v>369</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C56" t="s">
         <v>370</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="5" t="s">
         <v>370</v>
       </c>
       <c r="E56"/>
-      <c r="F56" t="s">
+      <c r="F56" s="5" t="s">
         <v>53</v>
       </c>
       <c r="G56"/>
@@ -6699,17 +7036,17 @@
       <c r="A57" t="s">
         <v>371</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C57" t="s">
         <v>372</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E57"/>
-      <c r="F57" t="s">
+      <c r="F57" s="5" t="s">
         <v>271</v>
       </c>
       <c r="G57"/>
@@ -6718,17 +7055,17 @@
       <c r="A58" t="s">
         <v>373</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C58" t="s">
         <v>374</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E58"/>
-      <c r="F58" t="s">
+      <c r="F58" s="5" t="s">
         <v>271</v>
       </c>
       <c r="G58"/>
@@ -6737,17 +7074,17 @@
       <c r="A59" t="s">
         <v>375</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C59" t="s">
         <v>376</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E59"/>
-      <c r="F59" t="s">
+      <c r="F59" s="5" t="s">
         <v>271</v>
       </c>
       <c r="G59"/>
@@ -6756,17 +7093,17 @@
       <c r="A60" t="s">
         <v>377</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C60" t="s">
         <v>378</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E60"/>
-      <c r="F60" t="s">
+      <c r="F60" s="5" t="s">
         <v>379</v>
       </c>
       <c r="G60"/>
@@ -6775,17 +7112,17 @@
       <c r="A61" t="s">
         <v>380</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C61" t="s">
         <v>381</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E61"/>
-      <c r="F61" t="s">
+      <c r="F61" s="5" t="s">
         <v>379</v>
       </c>
       <c r="G61"/>
@@ -6794,17 +7131,17 @@
       <c r="A62" t="s">
         <v>382</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C62" t="s">
         <v>383</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E62"/>
-      <c r="F62" t="s">
+      <c r="F62" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G62"/>
@@ -6813,17 +7150,17 @@
       <c r="A63" t="s">
         <v>385</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C63" t="s">
         <v>386</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E63"/>
-      <c r="F63" t="s">
+      <c r="F63" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G63"/>
@@ -6832,17 +7169,17 @@
       <c r="A64" t="s">
         <v>387</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C64" t="s">
         <v>388</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E64"/>
-      <c r="F64" t="s">
+      <c r="F64" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G64"/>
@@ -6851,17 +7188,17 @@
       <c r="A65" t="s">
         <v>389</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C65" t="s">
         <v>390</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E65"/>
-      <c r="F65" t="s">
+      <c r="F65" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G65"/>
@@ -6870,17 +7207,17 @@
       <c r="A66" t="s">
         <v>391</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="5" t="s">
         <v>212</v>
       </c>
       <c r="C66" t="s">
         <v>392</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E66"/>
-      <c r="F66" t="s">
+      <c r="F66" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G66"/>
@@ -6889,17 +7226,17 @@
       <c r="A67" t="s">
         <v>393</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="5" t="s">
         <v>212</v>
       </c>
       <c r="C67" t="s">
         <v>394</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E67"/>
-      <c r="F67" t="s">
+      <c r="F67" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G67"/>
@@ -6908,17 +7245,17 @@
       <c r="A68" t="s">
         <v>395</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="5" t="s">
         <v>212</v>
       </c>
       <c r="C68" t="s">
         <v>396</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E68"/>
-      <c r="F68" t="s">
+      <c r="F68" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G68"/>
@@ -6927,17 +7264,17 @@
       <c r="A69" t="s">
         <v>397</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="5" t="s">
         <v>212</v>
       </c>
       <c r="C69" t="s">
         <v>398</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E69"/>
-      <c r="F69" t="s">
+      <c r="F69" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G69"/>
@@ -6946,17 +7283,17 @@
       <c r="A70" t="s">
         <v>399</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="5" t="s">
         <v>212</v>
       </c>
       <c r="C70" t="s">
         <v>400</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E70"/>
-      <c r="F70" t="s">
+      <c r="F70" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G70"/>
@@ -6965,17 +7302,17 @@
       <c r="A71" t="s">
         <v>401</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="5" t="s">
         <v>212</v>
       </c>
       <c r="C71" t="s">
         <v>402</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E71"/>
-      <c r="F71" t="s">
+      <c r="F71" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G71"/>
@@ -6984,17 +7321,17 @@
       <c r="A72" t="s">
         <v>403</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="5" t="s">
         <v>212</v>
       </c>
       <c r="C72" t="s">
         <v>404</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E72"/>
-      <c r="F72" t="s">
+      <c r="F72" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G72"/>
@@ -7003,17 +7340,17 @@
       <c r="A73" t="s">
         <v>405</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="5" t="s">
         <v>212</v>
       </c>
       <c r="C73" t="s">
         <v>406</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E73"/>
-      <c r="F73" t="s">
+      <c r="F73" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G73"/>
@@ -7022,17 +7359,17 @@
       <c r="A74" t="s">
         <v>407</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C74" t="s">
         <v>408</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E74"/>
-      <c r="F74" t="s">
+      <c r="F74" s="5" t="s">
         <v>178</v>
       </c>
       <c r="G74"/>
@@ -7041,17 +7378,17 @@
       <c r="A75" t="s">
         <v>409</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C75" t="s">
         <v>408</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E75"/>
-      <c r="F75" t="s">
+      <c r="F75" s="5" t="s">
         <v>178</v>
       </c>
       <c r="G75"/>
@@ -7060,17 +7397,17 @@
       <c r="A76" t="s">
         <v>410</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C76" t="s">
         <v>408</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E76"/>
-      <c r="F76" t="s">
+      <c r="F76" s="5" t="s">
         <v>178</v>
       </c>
       <c r="G76"/>
@@ -7079,17 +7416,17 @@
       <c r="A77" t="s">
         <v>411</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C77" t="s">
         <v>408</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E77"/>
-      <c r="F77" t="s">
+      <c r="F77" s="5" t="s">
         <v>178</v>
       </c>
       <c r="G77"/>
@@ -7098,17 +7435,17 @@
       <c r="A78" t="s">
         <v>412</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C78" t="s">
         <v>413</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E78"/>
-      <c r="F78" t="s">
+      <c r="F78" s="5" t="s">
         <v>178</v>
       </c>
       <c r="G78"/>
@@ -7117,17 +7454,17 @@
       <c r="A79" t="s">
         <v>414</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C79" t="s">
         <v>415</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E79"/>
-      <c r="F79" t="s">
+      <c r="F79" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G79"/>
@@ -7136,17 +7473,17 @@
       <c r="A80" t="s">
         <v>416</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C80" t="s">
         <v>417</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E80"/>
-      <c r="F80" t="s">
+      <c r="F80" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G80"/>
@@ -7155,17 +7492,17 @@
       <c r="A81" t="s">
         <v>418</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C81" t="s">
         <v>419</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E81"/>
-      <c r="F81" t="s">
+      <c r="F81" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G81"/>
@@ -7174,17 +7511,17 @@
       <c r="A82" t="s">
         <v>420</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C82" t="s">
         <v>421</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E82"/>
-      <c r="F82" t="s">
+      <c r="F82" s="5" t="s">
         <v>240</v>
       </c>
       <c r="G82" t="b">
@@ -7195,17 +7532,17 @@
       <c r="A83" t="s">
         <v>422</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C83" t="s">
         <v>423</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E83"/>
-      <c r="F83" t="s">
+      <c r="F83" s="5" t="s">
         <v>424</v>
       </c>
       <c r="G83" t="b">
@@ -7216,17 +7553,17 @@
       <c r="A84" t="s">
         <v>425</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C84" t="s">
         <v>426</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E84"/>
-      <c r="F84" t="s">
+      <c r="F84" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G84"/>
@@ -7235,17 +7572,17 @@
       <c r="A85" t="s">
         <v>427</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C85" t="s">
         <v>428</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E85"/>
-      <c r="F85" t="s">
+      <c r="F85" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G85"/>
@@ -7254,17 +7591,17 @@
       <c r="A86" t="s">
         <v>429</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C86" t="s">
         <v>430</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E86"/>
-      <c r="F86" t="s">
+      <c r="F86" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G86"/>
@@ -7273,17 +7610,17 @@
       <c r="A87" t="s">
         <v>431</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C87" t="s">
         <v>432</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E87"/>
-      <c r="F87" t="s">
+      <c r="F87" s="5" t="s">
         <v>433</v>
       </c>
       <c r="G87" t="b">
@@ -7294,17 +7631,17 @@
       <c r="A88" t="s">
         <v>434</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C88" t="s">
         <v>302</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E88"/>
-      <c r="F88" t="s">
+      <c r="F88" s="5" t="s">
         <v>433</v>
       </c>
       <c r="G88" t="b">
@@ -7315,17 +7652,17 @@
       <c r="A89" t="s">
         <v>435</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C89" t="s">
         <v>436</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E89"/>
-      <c r="F89" t="s">
+      <c r="F89" s="5" t="s">
         <v>433</v>
       </c>
       <c r="G89"/>
@@ -7334,28 +7671,31 @@
       <c r="A90" t="s">
         <v>437</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C90" t="s">
         <v>438</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E90"/>
-      <c r="F90" t="s">
+      <c r="F90" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G90"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -7395,17 +7735,17 @@
       <c r="A2" t="s">
         <v>439</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C2" t="s">
         <v>440</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="6" t="s">
         <v>441</v>
       </c>
       <c r="E2"/>
-      <c r="F2" t="s">
+      <c r="F2" s="6" t="s">
         <v>279</v>
       </c>
       <c r="G2"/>
@@ -7414,17 +7754,17 @@
       <c r="A3" t="s">
         <v>442</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C3" t="s">
         <v>443</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="6" t="s">
         <v>444</v>
       </c>
       <c r="E3"/>
-      <c r="F3" t="s">
+      <c r="F3" s="6" t="s">
         <v>445</v>
       </c>
       <c r="G3"/>
@@ -7433,17 +7773,17 @@
       <c r="A4" t="s">
         <v>446</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C4" t="s">
         <v>447</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="6" t="s">
         <v>448</v>
       </c>
       <c r="E4"/>
-      <c r="F4" t="s">
+      <c r="F4" s="6" t="s">
         <v>224</v>
       </c>
       <c r="G4"/>
@@ -7452,15 +7792,15 @@
       <c r="A5" t="s">
         <v>449</v>
       </c>
-      <c r="B5"/>
+      <c r="B5" s="6"/>
       <c r="C5" t="s">
         <v>450</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E5"/>
-      <c r="F5" t="s">
+      <c r="F5" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G5"/>
@@ -7469,15 +7809,15 @@
       <c r="A6" t="s">
         <v>451</v>
       </c>
-      <c r="B6"/>
+      <c r="B6" s="6"/>
       <c r="C6" t="s">
         <v>452</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E6"/>
-      <c r="F6" t="s">
+      <c r="F6" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G6"/>
@@ -7486,15 +7826,15 @@
       <c r="A7" t="s">
         <v>453</v>
       </c>
-      <c r="B7"/>
+      <c r="B7" s="6"/>
       <c r="C7" t="s">
         <v>454</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E7"/>
-      <c r="F7" t="s">
+      <c r="F7" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G7"/>
@@ -7503,17 +7843,17 @@
       <c r="A8" t="s">
         <v>455</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C8" t="s">
         <v>456</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E8"/>
-      <c r="F8" t="s">
+      <c r="F8" s="6" t="s">
         <v>457</v>
       </c>
       <c r="G8"/>
@@ -7522,17 +7862,17 @@
       <c r="A9" t="s">
         <v>458</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C9" t="s">
         <v>459</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E9"/>
-      <c r="F9" t="s">
+      <c r="F9" s="6" t="s">
         <v>460</v>
       </c>
       <c r="G9"/>
@@ -7541,17 +7881,17 @@
       <c r="A10" t="s">
         <v>461</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C10" t="s">
         <v>462</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E10"/>
-      <c r="F10" t="s">
+      <c r="F10" s="6" t="s">
         <v>463</v>
       </c>
       <c r="G10"/>
@@ -7560,17 +7900,17 @@
       <c r="A11" t="s">
         <v>464</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C11" t="s">
         <v>465</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E11"/>
-      <c r="F11" t="s">
+      <c r="F11" s="6" t="s">
         <v>466</v>
       </c>
       <c r="G11"/>
@@ -7579,17 +7919,17 @@
       <c r="A12" t="s">
         <v>467</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C12" t="s">
         <v>468</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E12"/>
-      <c r="F12" t="s">
+      <c r="F12" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G12"/>
@@ -7598,17 +7938,17 @@
       <c r="A13" t="s">
         <v>469</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C13" t="s">
         <v>470</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E13"/>
-      <c r="F13" t="s">
+      <c r="F13" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G13"/>
@@ -7617,17 +7957,17 @@
       <c r="A14" t="s">
         <v>471</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C14" t="s">
         <v>472</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E14"/>
-      <c r="F14" t="s">
+      <c r="F14" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G14"/>
@@ -7636,17 +7976,17 @@
       <c r="A15" t="s">
         <v>473</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C15" t="s">
         <v>474</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E15"/>
-      <c r="F15" t="s">
+      <c r="F15" s="6" t="s">
         <v>463</v>
       </c>
       <c r="G15"/>
@@ -7655,17 +7995,17 @@
       <c r="A16" t="s">
         <v>475</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C16" t="s">
         <v>476</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E16"/>
-      <c r="F16" t="s">
+      <c r="F16" s="6" t="s">
         <v>463</v>
       </c>
       <c r="G16"/>
@@ -7674,17 +8014,17 @@
       <c r="A17" t="s">
         <v>477</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C17" t="s">
         <v>478</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E17"/>
-      <c r="F17" t="s">
+      <c r="F17" s="6" t="s">
         <v>463</v>
       </c>
       <c r="G17"/>
@@ -7693,17 +8033,17 @@
       <c r="A18" t="s">
         <v>479</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C18" t="s">
         <v>480</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E18"/>
-      <c r="F18" t="s">
+      <c r="F18" s="6" t="s">
         <v>463</v>
       </c>
       <c r="G18"/>
@@ -7712,17 +8052,17 @@
       <c r="A19" t="s">
         <v>481</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
         <v>482</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E19"/>
-      <c r="F19" t="s">
+      <c r="F19" s="6" t="s">
         <v>463</v>
       </c>
       <c r="G19"/>
@@ -7731,17 +8071,17 @@
       <c r="A20" t="s">
         <v>483</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
         <v>484</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E20"/>
-      <c r="F20" t="s">
+      <c r="F20" s="6" t="s">
         <v>463</v>
       </c>
       <c r="G20"/>
@@ -7750,17 +8090,17 @@
       <c r="A21" t="s">
         <v>485</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C21" t="s">
         <v>486</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E21"/>
-      <c r="F21" t="s">
+      <c r="F21" s="6" t="s">
         <v>463</v>
       </c>
       <c r="G21"/>
@@ -7769,17 +8109,17 @@
       <c r="A22" t="s">
         <v>487</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C22" t="s">
         <v>488</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E22"/>
-      <c r="F22" t="s">
+      <c r="F22" s="6" t="s">
         <v>463</v>
       </c>
       <c r="G22"/>
@@ -7788,17 +8128,17 @@
       <c r="A23" t="s">
         <v>489</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" t="s">
         <v>490</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E23"/>
-      <c r="F23" t="s">
+      <c r="F23" s="6" t="s">
         <v>463</v>
       </c>
       <c r="G23"/>
@@ -7807,17 +8147,17 @@
       <c r="A24" t="s">
         <v>491</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C24" t="s">
         <v>492</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="6" t="s">
         <v>493</v>
       </c>
       <c r="E24"/>
-      <c r="F24" t="s">
+      <c r="F24" s="6" t="s">
         <v>494</v>
       </c>
       <c r="G24"/>
@@ -7826,17 +8166,17 @@
       <c r="A25" t="s">
         <v>495</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C25" t="s">
         <v>496</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="6" t="s">
         <v>497</v>
       </c>
       <c r="E25"/>
-      <c r="F25" t="s">
+      <c r="F25" s="6" t="s">
         <v>279</v>
       </c>
       <c r="G25"/>
@@ -7845,17 +8185,17 @@
       <c r="A26" t="s">
         <v>498</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C26" t="s">
         <v>499</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="6" t="s">
         <v>500</v>
       </c>
       <c r="E26"/>
-      <c r="F26" t="s">
+      <c r="F26" s="6" t="s">
         <v>501</v>
       </c>
       <c r="G26"/>
@@ -7864,17 +8204,17 @@
       <c r="A27" t="s">
         <v>502</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C27" t="s">
         <v>503</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="6" t="s">
         <v>504</v>
       </c>
       <c r="E27"/>
-      <c r="F27" t="s">
+      <c r="F27" s="6" t="s">
         <v>279</v>
       </c>
       <c r="G27"/>
@@ -7883,17 +8223,17 @@
       <c r="A28" t="s">
         <v>505</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C28" t="s">
         <v>506</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="6" t="s">
         <v>507</v>
       </c>
       <c r="E28"/>
-      <c r="F28" t="s">
+      <c r="F28" s="6" t="s">
         <v>508</v>
       </c>
       <c r="G28"/>
@@ -7902,17 +8242,17 @@
       <c r="A29" t="s">
         <v>509</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C29" t="s">
         <v>510</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="6" t="s">
         <v>511</v>
       </c>
       <c r="E29"/>
-      <c r="F29" t="s">
+      <c r="F29" s="6" t="s">
         <v>279</v>
       </c>
       <c r="G29"/>
@@ -7921,17 +8261,17 @@
       <c r="A30" t="s">
         <v>512</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C30" t="s">
         <v>513</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="6" t="s">
         <v>514</v>
       </c>
       <c r="E30"/>
-      <c r="F30" t="s">
+      <c r="F30" s="6" t="s">
         <v>501</v>
       </c>
       <c r="G30"/>
@@ -7940,17 +8280,17 @@
       <c r="A31" t="s">
         <v>515</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C31" t="s">
         <v>516</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="6" t="s">
         <v>517</v>
       </c>
       <c r="E31"/>
-      <c r="F31" t="s">
+      <c r="F31" s="6" t="s">
         <v>501</v>
       </c>
       <c r="G31"/>
@@ -7959,17 +8299,17 @@
       <c r="A32" t="s">
         <v>518</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="6" t="s">
         <v>519</v>
       </c>
       <c r="C32" t="s">
         <v>520</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="6" t="s">
         <v>521</v>
       </c>
       <c r="E32"/>
-      <c r="F32" t="s">
+      <c r="F32" s="6" t="s">
         <v>522</v>
       </c>
       <c r="G32"/>
@@ -7978,17 +8318,17 @@
       <c r="A33" t="s">
         <v>523</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C33" t="s">
         <v>524</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="6" t="s">
         <v>525</v>
       </c>
       <c r="E33"/>
-      <c r="F33" t="s">
+      <c r="F33" s="6" t="s">
         <v>522</v>
       </c>
       <c r="G33"/>
@@ -7997,17 +8337,17 @@
       <c r="A34" t="s">
         <v>526</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C34" t="s">
         <v>527</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="6" t="s">
         <v>528</v>
       </c>
       <c r="E34"/>
-      <c r="F34" t="s">
+      <c r="F34" s="6" t="s">
         <v>522</v>
       </c>
       <c r="G34"/>
@@ -8016,17 +8356,17 @@
       <c r="A35" t="s">
         <v>529</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C35" t="s">
         <v>530</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="6" t="s">
         <v>531</v>
       </c>
       <c r="E35"/>
-      <c r="F35" t="s">
+      <c r="F35" s="6" t="s">
         <v>522</v>
       </c>
       <c r="G35"/>
@@ -8035,17 +8375,17 @@
       <c r="A36" t="s">
         <v>532</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C36" t="s">
         <v>533</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="6" t="s">
         <v>534</v>
       </c>
       <c r="E36"/>
-      <c r="F36" t="s">
+      <c r="F36" s="6" t="s">
         <v>279</v>
       </c>
       <c r="G36"/>
@@ -8054,17 +8394,17 @@
       <c r="A37" t="s">
         <v>535</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C37" t="s">
         <v>536</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="6" t="s">
         <v>537</v>
       </c>
       <c r="E37"/>
-      <c r="F37" t="s">
+      <c r="F37" s="6" t="s">
         <v>240</v>
       </c>
       <c r="G37"/>
@@ -8073,17 +8413,17 @@
       <c r="A38" t="s">
         <v>538</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C38" t="s">
         <v>539</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E38"/>
-      <c r="F38" t="s">
+      <c r="F38" s="6" t="s">
         <v>384</v>
       </c>
       <c r="G38"/>
@@ -8092,17 +8432,17 @@
       <c r="A39" t="s">
         <v>540</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" t="s">
         <v>541</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E39"/>
-      <c r="F39" t="s">
+      <c r="F39" s="6" t="s">
         <v>384</v>
       </c>
       <c r="G39"/>
@@ -8111,28 +8451,31 @@
       <c r="A40" t="s">
         <v>542</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="6" t="s">
         <v>543</v>
       </c>
       <c r="C40" t="s">
         <v>544</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E40"/>
-      <c r="F40" t="s">
+      <c r="F40" s="6" t="s">
         <v>384</v>
       </c>
       <c r="G40"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -8172,19 +8515,19 @@
       <c r="A2" t="s">
         <v>545</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="7" t="s">
         <v>39</v>
       </c>
       <c r="C2" t="s">
         <v>546</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G2"/>
@@ -8193,19 +8536,19 @@
       <c r="A3" t="s">
         <v>130</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="7" t="s">
         <v>131</v>
       </c>
       <c r="C3" t="s">
         <v>132</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G3"/>
@@ -8214,17 +8557,17 @@
       <c r="A4" t="s">
         <v>185</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E4"/>
-      <c r="F4" t="s">
+      <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G4"/>
@@ -8233,17 +8576,17 @@
       <c r="A5" t="s">
         <v>186</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E5"/>
-      <c r="F5" t="s">
+      <c r="F5" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G5"/>
@@ -8252,17 +8595,17 @@
       <c r="A6" t="s">
         <v>187</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E6"/>
-      <c r="F6" t="s">
+      <c r="F6" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G6"/>
@@ -8271,19 +8614,19 @@
       <c r="A7" t="s">
         <v>123</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>124</v>
       </c>
       <c r="C7" t="s">
         <v>547</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G7"/>
@@ -8292,19 +8635,19 @@
       <c r="A8" t="s">
         <v>548</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="7" t="s">
         <v>549</v>
       </c>
       <c r="C8" t="s">
         <v>550</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G8"/>
@@ -8313,17 +8656,17 @@
       <c r="A9" t="s">
         <v>551</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="7" t="s">
         <v>46</v>
       </c>
       <c r="C9" t="s">
         <v>552</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E9"/>
-      <c r="F9" t="s">
+      <c r="F9" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G9"/>
@@ -8332,17 +8675,17 @@
       <c r="A10" t="s">
         <v>553</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="7" t="s">
         <v>39</v>
       </c>
       <c r="C10" t="s">
         <v>554</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E10"/>
-      <c r="F10" t="s">
+      <c r="F10" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G10"/>
@@ -8351,17 +8694,17 @@
       <c r="A11" t="s">
         <v>555</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="7" t="s">
         <v>556</v>
       </c>
       <c r="C11" t="s">
         <v>557</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="7" t="s">
         <v>558</v>
       </c>
       <c r="E11"/>
-      <c r="F11" t="s">
+      <c r="F11" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G11"/>
@@ -8370,17 +8713,17 @@
       <c r="A12" t="s">
         <v>559</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="7" t="s">
         <v>560</v>
       </c>
       <c r="C12" t="s">
         <v>561</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E12"/>
-      <c r="F12" t="s">
+      <c r="F12" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G12"/>
@@ -8389,17 +8732,17 @@
       <c r="A13" t="s">
         <v>562</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="7" t="s">
         <v>563</v>
       </c>
       <c r="C13" t="s">
         <v>564</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E13"/>
-      <c r="F13" t="s">
+      <c r="F13" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G13"/>
@@ -8408,17 +8751,17 @@
       <c r="A14" t="s">
         <v>565</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="7" t="s">
         <v>566</v>
       </c>
       <c r="C14" t="s">
         <v>567</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="7" t="s">
         <v>568</v>
       </c>
       <c r="E14"/>
-      <c r="F14" t="s">
+      <c r="F14" s="7" t="s">
         <v>569</v>
       </c>
       <c r="G14"/>
@@ -8427,17 +8770,17 @@
       <c r="A15" t="s">
         <v>570</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C15" t="s">
         <v>571</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E15"/>
-      <c r="F15" t="s">
+      <c r="F15" s="7" t="s">
         <v>569</v>
       </c>
       <c r="G15"/>
@@ -8446,17 +8789,17 @@
       <c r="A16" t="s">
         <v>572</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="7" t="s">
         <v>39</v>
       </c>
       <c r="C16" t="s">
         <v>573</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E16"/>
-      <c r="F16" t="s">
+      <c r="F16" s="7" t="s">
         <v>569</v>
       </c>
       <c r="G16"/>
@@ -8465,17 +8808,17 @@
       <c r="A17" t="s">
         <v>574</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="7" t="s">
         <v>131</v>
       </c>
       <c r="C17" t="s">
         <v>575</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E17"/>
-      <c r="F17" t="s">
+      <c r="F17" s="7" t="s">
         <v>569</v>
       </c>
       <c r="G17"/>
@@ -8484,17 +8827,17 @@
       <c r="A18" t="s">
         <v>576</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C18" t="s">
         <v>577</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E18"/>
-      <c r="F18" t="s">
+      <c r="F18" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G18"/>
@@ -8503,17 +8846,17 @@
       <c r="A19" t="s">
         <v>578</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="7" t="s">
         <v>579</v>
       </c>
       <c r="C19" t="s">
         <v>580</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="7" t="s">
         <v>581</v>
       </c>
       <c r="E19"/>
-      <c r="F19" t="s">
+      <c r="F19" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G19"/>
@@ -8522,17 +8865,17 @@
       <c r="A20" t="s">
         <v>582</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="7" t="s">
         <v>549</v>
       </c>
       <c r="C20" t="s">
         <v>583</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E20"/>
-      <c r="F20" t="s">
+      <c r="F20" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G20"/>
@@ -8541,28 +8884,31 @@
       <c r="A21" t="s">
         <v>584</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="7" t="s">
         <v>131</v>
       </c>
       <c r="C21" t="s">
         <v>585</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E21"/>
-      <c r="F21" t="s">
+      <c r="F21" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G21"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -8602,19 +8948,19 @@
       <c r="A2" t="s">
         <v>123</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>124</v>
       </c>
       <c r="C2" t="s">
         <v>586</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G2"/>
@@ -8623,17 +8969,17 @@
       <c r="A3" t="s">
         <v>110</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>46</v>
       </c>
       <c r="C3" t="s">
         <v>111</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E3"/>
-      <c r="F3" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G3"/>
@@ -8642,19 +8988,19 @@
       <c r="A4" t="s">
         <v>587</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C4" t="s">
         <v>588</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="8" t="s">
         <v>589</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G4"/>
@@ -8663,19 +9009,19 @@
       <c r="A5" t="s">
         <v>590</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>131</v>
       </c>
       <c r="C5" t="s">
         <v>591</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G5"/>
@@ -8684,19 +9030,19 @@
       <c r="A6" t="s">
         <v>592</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>593</v>
       </c>
       <c r="C6" t="s">
         <v>594</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="8" t="s">
         <v>595</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G6"/>
@@ -8705,17 +9051,17 @@
       <c r="A7" t="s">
         <v>596</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>597</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="8" t="s">
         <v>598</v>
       </c>
       <c r="E7"/>
-      <c r="F7" t="s">
+      <c r="F7" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G7"/>
@@ -8724,17 +9070,17 @@
       <c r="A8" t="s">
         <v>190</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="8" t="s">
         <v>191</v>
       </c>
       <c r="C8" t="s">
         <v>191</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E8"/>
-      <c r="F8" t="s">
+      <c r="F8" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G8"/>
@@ -8743,17 +9089,17 @@
       <c r="A9" t="s">
         <v>185</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E9"/>
-      <c r="F9" t="s">
+      <c r="F9" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G9"/>
@@ -8762,17 +9108,17 @@
       <c r="A10" t="s">
         <v>186</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E10"/>
-      <c r="F10" t="s">
+      <c r="F10" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G10"/>
@@ -8781,28 +9127,31 @@
       <c r="A11" t="s">
         <v>187</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E11"/>
-      <c r="F11" t="s">
+      <c r="F11" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G11"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -8842,19 +9191,19 @@
       <c r="A2" t="s">
         <v>599</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="9" t="s">
         <v>549</v>
       </c>
       <c r="C2" t="s">
         <v>600</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G2"/>
@@ -8863,17 +9212,17 @@
       <c r="A3" t="s">
         <v>601</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>602</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E3"/>
-      <c r="F3" t="s">
+      <c r="F3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G3"/>
@@ -8882,17 +9231,17 @@
       <c r="A4" t="s">
         <v>603</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>604</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E4"/>
-      <c r="F4" t="s">
+      <c r="F4" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G4"/>
@@ -8901,19 +9250,19 @@
       <c r="A5" t="s">
         <v>605</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C5" t="s">
         <v>606</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="9" t="s">
         <v>607</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G5"/>
@@ -8922,19 +9271,19 @@
       <c r="A6" t="s">
         <v>545</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C6" t="s">
         <v>129</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G6"/>
@@ -8943,19 +9292,19 @@
       <c r="A7" t="s">
         <v>130</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="9" t="s">
         <v>131</v>
       </c>
       <c r="C7" t="s">
         <v>132</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G7"/>
@@ -8964,17 +9313,17 @@
       <c r="A8" t="s">
         <v>185</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E8"/>
-      <c r="F8" t="s">
+      <c r="F8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G8"/>
@@ -8983,17 +9332,17 @@
       <c r="A9" t="s">
         <v>186</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E9"/>
-      <c r="F9" t="s">
+      <c r="F9" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G9"/>
@@ -9002,17 +9351,17 @@
       <c r="A10" t="s">
         <v>187</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E10"/>
-      <c r="F10" t="s">
+      <c r="F10" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G10"/>
@@ -9021,19 +9370,19 @@
       <c r="A11" t="s">
         <v>608</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="9" t="s">
         <v>609</v>
       </c>
       <c r="C11" t="s">
         <v>610</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G11"/>
@@ -9042,17 +9391,17 @@
       <c r="A12" t="s">
         <v>611</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
         <v>612</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E12"/>
-      <c r="F12" t="s">
+      <c r="F12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G12"/>
@@ -9061,19 +9410,19 @@
       <c r="A13" t="s">
         <v>613</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="9" t="s">
         <v>86</v>
       </c>
       <c r="C13" t="s">
         <v>614</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G13"/>
@@ -9082,17 +9431,17 @@
       <c r="A14" t="s">
         <v>615</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
         <v>616</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E14"/>
-      <c r="F14" t="s">
+      <c r="F14" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G14"/>
@@ -9101,17 +9450,17 @@
       <c r="A15" t="s">
         <v>617</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C15" t="s">
         <v>618</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E15"/>
-      <c r="F15" t="s">
+      <c r="F15" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G15"/>
@@ -9120,17 +9469,17 @@
       <c r="A16" t="s">
         <v>619</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
         <v>620</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E16"/>
-      <c r="F16" t="s">
+      <c r="F16" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G16"/>
@@ -9139,17 +9488,17 @@
       <c r="A17" t="s">
         <v>621</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C17" t="s">
         <v>622</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E17"/>
-      <c r="F17" t="s">
+      <c r="F17" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G17"/>
@@ -9158,17 +9507,17 @@
       <c r="A18" t="s">
         <v>623</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="9" t="s">
         <v>624</v>
       </c>
       <c r="C18" t="s">
         <v>625</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E18"/>
-      <c r="F18" t="s">
+      <c r="F18" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G18"/>
@@ -9177,17 +9526,17 @@
       <c r="A19" t="s">
         <v>626</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C19" t="s">
         <v>627</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E19"/>
-      <c r="F19" t="s">
+      <c r="F19" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G19"/>
@@ -9196,17 +9545,17 @@
       <c r="A20" t="s">
         <v>628</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
         <v>629</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E20"/>
-      <c r="F20" t="s">
+      <c r="F20" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G20"/>
@@ -9215,17 +9564,17 @@
       <c r="A21" t="s">
         <v>630</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="9" t="s">
         <v>631</v>
       </c>
       <c r="C21" t="s">
         <v>632</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E21"/>
-      <c r="F21" t="s">
+      <c r="F21" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G21"/>
@@ -9234,17 +9583,17 @@
       <c r="A22" t="s">
         <v>633</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="9" t="s">
         <v>634</v>
       </c>
       <c r="C22" t="s">
         <v>635</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E22"/>
-      <c r="F22" t="s">
+      <c r="F22" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G22"/>
@@ -9253,17 +9602,17 @@
       <c r="A23" t="s">
         <v>636</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="9" t="s">
         <v>637</v>
       </c>
       <c r="C23" t="s">
         <v>17</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E23"/>
-      <c r="F23" t="s">
+      <c r="F23" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G23"/>
@@ -9272,17 +9621,17 @@
       <c r="A24" t="s">
         <v>638</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="9" t="s">
         <v>212</v>
       </c>
       <c r="C24" t="s">
         <v>639</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E24"/>
-      <c r="F24" t="s">
+      <c r="F24" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G24"/>
@@ -9291,22 +9640,25 @@
       <c r="A25" t="s">
         <v>640</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="9" t="s">
         <v>212</v>
       </c>
       <c r="C25" t="s">
         <v>641</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E25"/>
-      <c r="F25" t="s">
+      <c r="F25" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G25"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>